--- a/docs/tiny_tpu_FV_Plan.xlsx
+++ b/docs/tiny_tpu_FV_Plan.xlsx
@@ -571,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I121"/>
+  <dimension ref="A1:I141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -994,7 +994,7 @@
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>PE-A07</t>
+          <t>PE-A06c</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>p_valid_out_registered</t>
+          <t>p_disabled_clears_switch_out</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>VP</t>
+          <t>RST</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
@@ -1019,17 +1019,17 @@
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>1'b1 |=&gt; pe_valid_out==$past(pe_valid_in)</t>
+          <t>!pe_enabled |=&gt; !pe_switch_out</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>BMC</t>
+          <t>Unbounded</t>
         </is>
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I11" s="8" t="inlineStr">
@@ -1041,7 +1041,7 @@
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>PE-A08</t>
+          <t>PE-A06d</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -1051,12 +1051,12 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>p_switch_out_registered</t>
+          <t>p_disabled_clears_weight_out</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>VP</t>
+          <t>RST</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>1'b1 |=&gt; pe_switch_out==$past(pe_switch_in)</t>
+          <t>!pe_enabled |=&gt; pe_weight_out==0</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>BMC</t>
+          <t>Unbounded</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
@@ -1088,7 +1088,7 @@
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>PE-A09</t>
+          <t>PE-A07</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>p_weight_out_when_accepting</t>
+          <t>p_valid_out_registered</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>DP</t>
+          <t>VP</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>pe_accept_w_in |=&gt; pe_weight_out==$past(pe_weight_in)</t>
+          <t>1'b1 |=&gt; pe_valid_out==$past(pe_valid_in)</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>PE-A10</t>
+          <t>PE-A08</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>p_weight_out_zero_when_not_accepting</t>
+          <t>p_switch_out_registered</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>DP</t>
+          <t>VP</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>!pe_accept_w_in |=&gt; pe_weight_out==0</t>
+          <t>1'b1 |=&gt; pe_switch_out==$past(pe_switch_in)</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1182,7 +1182,7 @@
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>PE-A11</t>
+          <t>PE-A09</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>p_input_out_captured_on_valid</t>
+          <t>p_weight_out_when_accepting</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>pe_valid_in |=&gt; pe_input_out==$past(pe_input_in)</t>
+          <t>pe_accept_w_in |=&gt; pe_weight_out==$past(pe_weight_in)</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
@@ -1229,7 +1229,7 @@
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>PE-A12</t>
+          <t>PE-A10</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>p_psum_zero_when_invalid</t>
+          <t>p_weight_out_zero_when_not_accepting</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>!pe_valid_in |=&gt; pe_psum_out==0</t>
+          <t>!pe_accept_w_in |=&gt; pe_weight_out==0</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -1276,7 +1276,7 @@
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>PE-A13</t>
+          <t>PE-A11</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>p_valid_out_low_when_in_low</t>
+          <t>p_input_out_captured_on_valid</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>VP</t>
+          <t>DP</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>!pe_valid_in |=&gt; !pe_valid_out</t>
+          <t>pe_valid_in |=&gt; pe_input_out==$past(pe_input_in)</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
@@ -1323,7 +1323,7 @@
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>PE-A14a</t>
+          <t>PE-A12</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -1333,32 +1333,32 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>p_rst_clears_weight_reg_active</t>
+          <t>p_psum_zero_when_invalid</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>RST</t>
+          <t>DP</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>(rst||!pe_enabled) |=&gt; weight_reg_active==0</t>
+          <t>!pe_valid_in |=&gt; pe_psum_out==0</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Unbounded</t>
+          <t>BMC</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I18" s="8" t="inlineStr">
@@ -1370,398 +1370,398 @@
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
+          <t>PE-A13</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>pe</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>p_valid_out_low_when_in_low</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>VP</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>!pe_valid_in |=&gt; !pe_valid_out</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>BMC</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>PE-A14a</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>pe</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>p_rst_clears_weight_reg_active</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>RST</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>(rst||!pe_enabled) |=&gt; weight_reg_active==0</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Unbounded</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
           <t>PE-A14b</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t>p_rst_clears_weight_reg_inactive</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>RST</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>(rst||!pe_enabled) |=&gt; weight_reg_inactive==0</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>Unbounded</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>PE-A15</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>pe</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>p_weight_switch</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>DP</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>pe_switch_in |=&gt; weight_reg_active==$past(weight_reg_inactive)</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>BMC</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>PE-A16</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>pe</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>p_input_out_clear_when_invalid</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>DP</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>!pe_valid_in |=&gt; pe_input_out==16'b0</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>BMC</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>PE-A17</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>pe</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>p_rst_clears_overflow</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>RST</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>(rst||!pe_enabled) |=&gt; !pe_overflow_out</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>Unbounded</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>PE-A18</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>pe</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>p_overflow_is_sticky</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>pe_overflow_out |=&gt; pe_overflow_out</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>BMC</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>PE-A19</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>pe</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>p_mac_zero_input_passthrough_psum</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr">
-        <is>
-          <t>(rst||!pe_enabled) |=&gt; weight_reg_inactive==0</t>
-        </is>
-      </c>
-      <c r="G19" s="9" t="inlineStr">
-        <is>
-          <t>Unbounded</t>
-        </is>
-      </c>
-      <c r="H19" s="9" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I19" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>(pe_valid_in &amp;&amp; pe_input_in==0) |=&gt; pe_psum_out==$past(pe_psum_in)  [port-observable MAC proxy; see PE-W01]</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>BMC</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>── SYSTOLIC ──</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n"/>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="n"/>
-      <c r="F20" s="2" t="n"/>
-      <c r="G20" s="2" t="n"/>
-      <c r="H20" s="2" t="n"/>
-      <c r="I20" s="3" t="n"/>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>SYS-A01</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>systolic</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>p_rst_clears_valid_out_21</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>RST</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>rst |=&gt; !sys_valid_out_21</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>Unbounded</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I21" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>SYS-A02</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>systolic</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>p_rst_clears_valid_out_22</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>RST</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F22" s="11" t="inlineStr">
-        <is>
-          <t>rst |=&gt; !sys_valid_out_22</t>
-        </is>
-      </c>
-      <c r="G22" s="9" t="inlineStr">
-        <is>
-          <t>Unbounded</t>
-        </is>
-      </c>
-      <c r="H22" s="9" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>SYS-A03</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>systolic</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>p_rst_clears_data_out_21</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>RST</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>rst |=&gt; sys_data_out_21==0</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>Unbounded</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I23" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>SYS-A04</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>systolic</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>p_rst_clears_data_out_22</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>RST</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F24" s="11" t="inlineStr">
-        <is>
-          <t>rst |=&gt; sys_data_out_22==0</t>
-        </is>
-      </c>
-      <c r="G24" s="9" t="inlineStr">
-        <is>
-          <t>Unbounded</t>
-        </is>
-      </c>
-      <c r="H24" s="9" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I24" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>SYS-A05</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>systolic</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>p_valid_21_one_cycle_delay</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>VP</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>sys_start_2 |=&gt; sys_valid_out_21</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>BMC</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I25" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>SYS-A06</t>
-        </is>
-      </c>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>systolic</t>
-        </is>
-      </c>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>p_valid_22_three_cycles_after_start1</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>VP</t>
-        </is>
-      </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F26" s="11" t="inlineStr">
-        <is>
-          <t>sys_start_1 |=&gt; ##2 sys_valid_out_22  [3 register stages: pe11→pe12→pe22]</t>
-        </is>
-      </c>
-      <c r="G26" s="9" t="inlineStr">
-        <is>
-          <t>BMC</t>
-        </is>
-      </c>
-      <c r="H26" s="9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I26" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>SYS-A07</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>systolic</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>p_valid_21_deasserts_after_start2</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>VP</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>$fell(sys_start_2) |=&gt; ##[0:1] $fell(sys_valid_out_21)</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>BMC</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I27" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
+      <c r="E27" s="2" t="n"/>
+      <c r="F27" s="2" t="n"/>
+      <c r="G27" s="2" t="n"/>
+      <c r="H27" s="2" t="n"/>
+      <c r="I27" s="3" t="n"/>
     </row>
     <row r="28" ht="28" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>SYS-A08</t>
+          <t>SYS-A01</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>p_col_size_1_disables_col2_valid</t>
+          <t>p_rst_clears_valid_out_21</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>ME</t>
+          <t>RST</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
@@ -1786,17 +1786,17 @@
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>(ub_rd_col_size_valid_in &amp;&amp; col_size==1) |=&gt; !sys_valid_out_22</t>
+          <t>rst |=&gt; !sys_valid_out_21</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
-          <t>BMC</t>
+          <t>Unbounded</t>
         </is>
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I28" s="8" t="inlineStr">
@@ -1808,7 +1808,7 @@
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>SYS-A09</t>
+          <t>SYS-A02</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -1818,32 +1818,32 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>p_col_size_2_both_outputs_reachable</t>
+          <t>p_rst_clears_valid_out_22</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>VP</t>
+          <t>RST</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>(col_size==2 &amp;&amp; start_1 &amp;&amp; start_2) |=&gt; ##[1:6] (valid_21 &amp;&amp; valid_22)</t>
+          <t>rst |=&gt; !sys_valid_out_22</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>BMC</t>
+          <t>Unbounded</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I29" s="8" t="inlineStr">
@@ -1855,7 +1855,7 @@
     <row r="30" ht="28" customHeight="1">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>SYS-A10</t>
+          <t>SYS-A03</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>p_rst_sets_pe_enabled_default</t>
+          <t>p_rst_clears_data_out_21</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="F30" s="11" t="inlineStr">
         <is>
-          <t>rst |=&gt; pe_enabled==2'b11</t>
+          <t>rst |=&gt; sys_data_out_21==0</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
@@ -1902,7 +1902,7 @@
     <row r="31" ht="28" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>SYS-A11</t>
+          <t>SYS-A04</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -1912,32 +1912,32 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>p_pe_enabled_mask_col_size_1</t>
+          <t>p_rst_clears_data_out_22</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>RST</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>(col_size_valid &amp;&amp; col_size==1) |=&gt; pe_enabled==2'b01</t>
+          <t>rst |=&gt; sys_data_out_22==0</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>BMC</t>
+          <t>Unbounded</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I31" s="8" t="inlineStr">
@@ -1949,995 +1949,1059 @@
     <row r="32" ht="28" customHeight="1">
       <c r="A32" s="9" t="inlineStr">
         <is>
+          <t>SYS-A05</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>systolic</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>p_valid_21_one_cycle_delay</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>VP</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>sys_start_2 |=&gt; sys_valid_out_21</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>BMC</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>SYS-A06</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>systolic</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>p_valid_22_three_cycles_after_start1</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>VP</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>sys_start_1 |=&gt; ##2 sys_valid_out_22  [3 register stages: pe11→pe12→pe22]</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>BMC</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>SYS-A07</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>systolic</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>p_valid_21_deasserts_after_start2</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>VP</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="inlineStr">
+        <is>
+          <t>$fell(sys_start_2) |=&gt; ##[0:1] $fell(sys_valid_out_21)</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>BMC</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I34" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>SYS-A08</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>systolic</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>p_col_size_1_disables_col2_valid</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>(ub_rd_col_size_valid_in &amp;&amp; col_size==1) |=&gt; !sys_valid_out_22</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>BMC</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I35" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>SYS-A09</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>systolic</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>p_col_size_2_both_outputs_reachable</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>VP</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="inlineStr">
+        <is>
+          <t>(col_size==2 &amp;&amp; start_1 &amp;&amp; start_2) |=&gt; ##[1:6] (valid_21 &amp;&amp; valid_22)</t>
+        </is>
+      </c>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>BMC</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I36" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>SYS-A10</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>systolic</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>p_rst_sets_pe_enabled_default</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>RST</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>rst |=&gt; pe_enabled==2'b11</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Unbounded</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I37" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>SYS-A11</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>systolic</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>p_pe_enabled_mask_col_size_1</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F38" s="11" t="inlineStr">
+        <is>
+          <t>(col_size_valid &amp;&amp; col_size==1) |=&gt; pe_enabled==2'b01</t>
+        </is>
+      </c>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>BMC</t>
+        </is>
+      </c>
+      <c r="H38" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
           <t>SYS-A12</t>
         </is>
       </c>
-      <c r="B32" s="10" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>systolic</t>
         </is>
       </c>
-      <c r="C32" s="10" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>p_pe_enabled_mask_col_size_2</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E32" s="9" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F32" s="11" t="inlineStr">
+      <c r="F39" s="7" t="inlineStr">
         <is>
           <t>(col_size_valid &amp;&amp; col_size==2) |=&gt; pe_enabled==2'b11</t>
         </is>
       </c>
-      <c r="G32" s="9" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>BMC</t>
         </is>
       </c>
-      <c r="H32" s="9" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I32" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>── BIAS_CHILD ──</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n"/>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n"/>
-      <c r="E33" s="2" t="n"/>
-      <c r="F33" s="2" t="n"/>
-      <c r="G33" s="2" t="n"/>
-      <c r="H33" s="2" t="n"/>
-      <c r="I33" s="3" t="n"/>
-    </row>
-    <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>BC-A01</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>bias_child</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>p_rst_clears_valid</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>RST</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F34" s="7" t="inlineStr">
-        <is>
-          <t>rst |=&gt; !bias_Z_valid_out</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>Unbounded</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I34" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="28" customHeight="1">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>BC-A02</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="inlineStr">
-        <is>
-          <t>bias_child</t>
-        </is>
-      </c>
-      <c r="C35" s="10" t="inlineStr">
-        <is>
-          <t>p_rst_clears_data</t>
-        </is>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>RST</t>
-        </is>
-      </c>
-      <c r="E35" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F35" s="11" t="inlineStr">
-        <is>
-          <t>rst |=&gt; bias_z_data_out==0</t>
-        </is>
-      </c>
-      <c r="G35" s="9" t="inlineStr">
-        <is>
-          <t>Unbounded</t>
-        </is>
-      </c>
-      <c r="H35" s="9" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I35" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>BC-A03</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>bias_child</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>p_valid_out_mirrors_valid_in</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>VP</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>1'b1 |=&gt; bias_Z_valid_out==$past(bias_sys_valid_in)</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>BMC</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I36" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="28" customHeight="1">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>BC-A04</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="inlineStr">
-        <is>
-          <t>bias_child</t>
-        </is>
-      </c>
-      <c r="C37" s="10" t="inlineStr">
-        <is>
-          <t>p_data_zero_when_invalid</t>
-        </is>
-      </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>DP</t>
-        </is>
-      </c>
-      <c r="E37" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F37" s="11" t="inlineStr">
-        <is>
-          <t>!bias_sys_valid_in |=&gt; bias_z_data_out==0</t>
-        </is>
-      </c>
-      <c r="G37" s="9" t="inlineStr">
-        <is>
-          <t>BMC</t>
-        </is>
-      </c>
-      <c r="H37" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I37" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="28" customHeight="1">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>BC-A05</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>bias_child</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>p_data_nonzero_when_both_inputs_nonzero</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>(valid_in &amp;&amp; data_in!=0 &amp;&amp; scalar!=0) |=&gt; bias_z_data_out!=0</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>BMC</t>
-        </is>
-      </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I38" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>── LEAKY_RELU_CHILD ──</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="n"/>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n"/>
-      <c r="E39" s="2" t="n"/>
-      <c r="F39" s="2" t="n"/>
-      <c r="G39" s="2" t="n"/>
-      <c r="H39" s="2" t="n"/>
-      <c r="I39" s="3" t="n"/>
+      <c r="I39" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="28" customHeight="1">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>LR-A01</t>
+          <t>SYS-A13</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>leaky_relu_child</t>
+          <t>systolic</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>p_rst_clears_outputs</t>
+          <t>p_col1_weight_load_no_col2_valid</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="inlineStr">
+        <is>
+          <t>(sys_accept_w_1 &amp;&amp; !sys_accept_w_2 &amp;&amp; !sys_start_1 &amp;&amp; !sys_start_2) |=&gt; !sys_valid_out_22  [col weight-load independence]</t>
+        </is>
+      </c>
+      <c r="G40" s="9" t="inlineStr">
+        <is>
+          <t>BMC</t>
+        </is>
+      </c>
+      <c r="H40" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>── BIAS_CHILD ──</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n"/>
+      <c r="E41" s="2" t="n"/>
+      <c r="F41" s="2" t="n"/>
+      <c r="G41" s="2" t="n"/>
+      <c r="H41" s="2" t="n"/>
+      <c r="I41" s="3" t="n"/>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>BC-A01</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>bias_child</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>p_rst_clears_valid</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
           <t>RST</t>
         </is>
       </c>
-      <c r="E40" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F40" s="11" t="inlineStr">
-        <is>
-          <t>rst |=&gt; (!lr_valid_out &amp;&amp; lr_data_out==0)</t>
-        </is>
-      </c>
-      <c r="G40" s="9" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>rst |=&gt; !bias_Z_valid_out</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>Unbounded</t>
         </is>
       </c>
-      <c r="H40" s="9" t="inlineStr">
+      <c r="H42" s="5" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="I40" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="28" customHeight="1">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>LR-A02</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>leaky_relu_child</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>p_valid_out_mirrors_input</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="I42" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="28" customHeight="1">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>BC-A02</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>bias_child</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>p_rst_clears_data</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>RST</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="inlineStr">
+        <is>
+          <t>rst |=&gt; bias_z_data_out==0</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>Unbounded</t>
+        </is>
+      </c>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I43" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>BC-A03</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>bias_child</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>p_valid_out_mirrors_valid_in</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>VP</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F41" s="7" t="inlineStr">
-        <is>
-          <t>1'b1 |=&gt; lr_valid_out==$past(lr_valid_in)  [gated: 0 when invalid]</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>1'b1 |=&gt; bias_Z_valid_out==$past(bias_sys_valid_in)</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>BMC</t>
         </is>
       </c>
-      <c r="H41" s="5" t="inlineStr">
+      <c r="H44" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I41" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="28" customHeight="1">
-      <c r="A42" s="9" t="inlineStr">
-        <is>
-          <t>LR-A03</t>
-        </is>
-      </c>
-      <c r="B42" s="10" t="inlineStr">
-        <is>
-          <t>leaky_relu_child</t>
-        </is>
-      </c>
-      <c r="C42" s="10" t="inlineStr">
+      <c r="I44" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>BC-A04</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>bias_child</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
         <is>
           <t>p_data_zero_when_invalid</t>
         </is>
       </c>
-      <c r="D42" s="9" t="inlineStr">
+      <c r="D45" s="9" t="inlineStr">
         <is>
           <t>DP</t>
         </is>
       </c>
-      <c r="E42" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F42" s="11" t="inlineStr">
-        <is>
-          <t>!lr_valid_in |=&gt; lr_data_out==0</t>
-        </is>
-      </c>
-      <c r="G42" s="9" t="inlineStr">
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F45" s="11" t="inlineStr">
+        <is>
+          <t>!bias_sys_valid_in |=&gt; bias_z_data_out==0</t>
+        </is>
+      </c>
+      <c r="G45" s="9" t="inlineStr">
         <is>
           <t>BMC</t>
         </is>
       </c>
-      <c r="H42" s="9" t="inlineStr">
+      <c r="H45" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I42" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="28" customHeight="1">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>LR-A04</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>leaky_relu_child</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>p_positive_input_passthrough</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="I45" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>BC-A05</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>bias_child</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>p_data_nonzero_when_both_inputs_nonzero</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>FA</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="inlineStr">
-        <is>
-          <t>(lr_valid_in &amp;&amp; lr_data_in&gt;=0) |=&gt; lr_data_out==$past(lr_data_in)</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>(valid_in &amp;&amp; data_in!=0 &amp;&amp; scalar!=0) |=&gt; bias_z_data_out!=0</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>BMC</t>
         </is>
       </c>
-      <c r="H43" s="5" t="inlineStr">
+      <c r="H46" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I43" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="28" customHeight="1">
-      <c r="A44" s="9" t="inlineStr">
-        <is>
-          <t>LR-A05</t>
-        </is>
-      </c>
-      <c r="B44" s="10" t="inlineStr">
-        <is>
-          <t>leaky_relu_child</t>
-        </is>
-      </c>
-      <c r="C44" s="10" t="inlineStr">
-        <is>
-          <t>p_negative_input_scaled</t>
-        </is>
-      </c>
-      <c r="D44" s="9" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
-      <c r="E44" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F44" s="11" t="inlineStr">
-        <is>
-          <t>(lr_valid_in &amp;&amp; lr_data_in[15] &amp;&amp; leak_factor!=1.0) |=&gt; lr_data_out!=$past(lr_data_in)</t>
-        </is>
-      </c>
-      <c r="G44" s="9" t="inlineStr">
-        <is>
-          <t>BMC</t>
-        </is>
-      </c>
-      <c r="H44" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I44" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="28" customHeight="1">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>LR-A06</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>leaky_relu_child</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>p_sign_preserved_for_positive</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>(lr_valid_in &amp;&amp; !lr_data_in[15]) |=&gt; !lr_data_out[15]</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="inlineStr">
-        <is>
-          <t>BMC</t>
-        </is>
-      </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I45" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="28" customHeight="1">
-      <c r="A46" s="9" t="inlineStr">
-        <is>
-          <t>LR-A07</t>
-        </is>
-      </c>
-      <c r="B46" s="10" t="inlineStr">
-        <is>
-          <t>leaky_relu_child</t>
-        </is>
-      </c>
-      <c r="C46" s="10" t="inlineStr">
-        <is>
-          <t>p_zero_boundary</t>
-        </is>
-      </c>
-      <c r="D46" s="9" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
-      <c r="E46" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F46" s="11" t="inlineStr">
-        <is>
-          <t>(lr_valid_in &amp;&amp; lr_data_in==0) |=&gt; lr_data_out==0</t>
-        </is>
-      </c>
-      <c r="G46" s="9" t="inlineStr">
-        <is>
-          <t>BMC</t>
-        </is>
-      </c>
-      <c r="H46" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="I46" s="8" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>── LRD_CHILD ──</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="n"/>
-      <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="n"/>
-      <c r="E47" s="2" t="n"/>
-      <c r="F47" s="2" t="n"/>
-      <c r="G47" s="2" t="n"/>
-      <c r="H47" s="2" t="n"/>
-      <c r="I47" s="3" t="n"/>
+    <row r="47" ht="28" customHeight="1">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>BC-A06</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>bias_child</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
+          <t>p_rst_clears_overflow</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>RST</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F47" s="11" t="inlineStr">
+        <is>
+          <t>rst |=&gt; !bias_overflow_out  [BUG-OVF-1: sticky flag cleared on reset]</t>
+        </is>
+      </c>
+      <c r="G47" s="9" t="inlineStr">
+        <is>
+          <t>Unbounded</t>
+        </is>
+      </c>
+      <c r="H47" s="9" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I47" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="28" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>LRD-A01</t>
+          <t>BC-A07</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>lrd_child</t>
+          <t>bias_child</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
+          <t>p_overflow_is_sticky</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>bias_overflow_out |=&gt; bias_overflow_out  [BUG-OVF-1: once set stays set until rst]</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>Unbounded</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I48" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>── LEAKY_RELU_CHILD ──</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n"/>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="n"/>
+      <c r="E49" s="2" t="n"/>
+      <c r="F49" s="2" t="n"/>
+      <c r="G49" s="2" t="n"/>
+      <c r="H49" s="2" t="n"/>
+      <c r="I49" s="3" t="n"/>
+    </row>
+    <row r="50" ht="28" customHeight="1">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>LR-A01</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>leaky_relu_child</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
           <t>p_rst_clears_outputs</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D50" s="9" t="inlineStr">
         <is>
           <t>RST</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F48" s="7" t="inlineStr">
-        <is>
-          <t>rst |=&gt; (!lr_d_valid_out &amp;&amp; lr_d_data_out==0)</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F50" s="11" t="inlineStr">
+        <is>
+          <t>rst |=&gt; (!lr_valid_out &amp;&amp; lr_data_out==0)</t>
+        </is>
+      </c>
+      <c r="G50" s="9" t="inlineStr">
         <is>
           <t>Unbounded</t>
         </is>
       </c>
-      <c r="H48" s="5" t="inlineStr">
+      <c r="H50" s="9" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="I48" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="28" customHeight="1">
-      <c r="A49" s="9" t="inlineStr">
-        <is>
-          <t>LRD-A02</t>
-        </is>
-      </c>
-      <c r="B49" s="10" t="inlineStr">
-        <is>
-          <t>lrd_child</t>
-        </is>
-      </c>
-      <c r="C49" s="10" t="inlineStr">
-        <is>
-          <t>p_valid_out_mirrors_valid_in</t>
-        </is>
-      </c>
-      <c r="D49" s="9" t="inlineStr">
+      <c r="I50" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>LR-A02</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>leaky_relu_child</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>p_valid_out_mirrors_input</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>VP</t>
         </is>
       </c>
-      <c r="E49" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F49" s="11" t="inlineStr">
-        <is>
-          <t>1'b1 |=&gt; lr_d_valid_out==$past(lr_d_valid_in)  [unconditional]</t>
-        </is>
-      </c>
-      <c r="G49" s="9" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>1'b1 |=&gt; lr_valid_out==$past(lr_valid_in)  [gated: 0 when invalid]</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>BMC</t>
         </is>
       </c>
-      <c r="H49" s="9" t="inlineStr">
+      <c r="H51" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I49" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="28" customHeight="1">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>LRD-A03</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>lrd_child</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
+      <c r="I51" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="28" customHeight="1">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>LR-A03</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>leaky_relu_child</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
         <is>
           <t>p_data_zero_when_invalid</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D52" s="9" t="inlineStr">
         <is>
           <t>DP</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F50" s="7" t="inlineStr">
-        <is>
-          <t>!lr_d_valid_in |=&gt; lr_d_data_out==0</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="E52" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F52" s="11" t="inlineStr">
+        <is>
+          <t>!lr_valid_in |=&gt; lr_data_out==0</t>
+        </is>
+      </c>
+      <c r="G52" s="9" t="inlineStr">
         <is>
           <t>BMC</t>
         </is>
       </c>
-      <c r="H50" s="5" t="inlineStr">
+      <c r="H52" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I50" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="28" customHeight="1">
-      <c r="A51" s="9" t="inlineStr">
-        <is>
-          <t>LRD-A04</t>
-        </is>
-      </c>
-      <c r="B51" s="10" t="inlineStr">
-        <is>
-          <t>lrd_child</t>
-        </is>
-      </c>
-      <c r="C51" s="10" t="inlineStr">
-        <is>
-          <t>p_positive_H_passes_gradient_through</t>
-        </is>
-      </c>
-      <c r="D51" s="9" t="inlineStr">
+      <c r="I52" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="28" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>LR-A04</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>leaky_relu_child</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>p_positive_input_passthrough</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>FA</t>
         </is>
       </c>
-      <c r="E51" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F51" s="11" t="inlineStr">
-        <is>
-          <t>(valid_in &amp;&amp; !H[15]) |=&gt; data_out==$past(data_in)</t>
-        </is>
-      </c>
-      <c r="G51" s="9" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>(lr_valid_in &amp;&amp; lr_data_in&gt;=0) |=&gt; lr_data_out==$past(lr_data_in)</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
         <is>
           <t>BMC</t>
         </is>
       </c>
-      <c r="H51" s="9" t="inlineStr">
+      <c r="H53" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I51" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="28" customHeight="1">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>LRD-A05</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>lrd_child</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>p_negative_H_scales_gradient</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="I53" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="28" customHeight="1">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>LR-A05</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>leaky_relu_child</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>p_negative_input_scaled</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
         <is>
           <t>FA</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F52" s="7" t="inlineStr">
-        <is>
-          <t>(valid_in &amp;&amp; H[15] &amp;&amp; leak!=1.0) |=&gt; data_out!=$past(data_in)</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F54" s="11" t="inlineStr">
+        <is>
+          <t>(lr_valid_in &amp;&amp; lr_data_in[15] &amp;&amp; leak_factor!=1.0) |=&gt; lr_data_out!=$past(lr_data_in)</t>
+        </is>
+      </c>
+      <c r="G54" s="9" t="inlineStr">
         <is>
           <t>BMC</t>
         </is>
       </c>
-      <c r="H52" s="5" t="inlineStr">
+      <c r="H54" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I52" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="28" customHeight="1">
-      <c r="A53" s="9" t="inlineStr">
-        <is>
-          <t>LRD-A06</t>
-        </is>
-      </c>
-      <c r="B53" s="10" t="inlineStr">
-        <is>
-          <t>lrd_child</t>
-        </is>
-      </c>
-      <c r="C53" s="10" t="inlineStr">
-        <is>
-          <t>p_zero_H_passes_gradient_through</t>
-        </is>
-      </c>
-      <c r="D53" s="9" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
-      <c r="E53" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F53" s="11" t="inlineStr">
-        <is>
-          <t>(valid_in &amp;&amp; H==0) |=&gt; data_out==$past(data_in)</t>
-        </is>
-      </c>
-      <c r="G53" s="9" t="inlineStr">
-        <is>
-          <t>BMC</t>
-        </is>
-      </c>
-      <c r="H53" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I53" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>── LOSS_CHILD ──</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="n"/>
-      <c r="C54" s="2" t="n"/>
-      <c r="D54" s="2" t="n"/>
-      <c r="E54" s="2" t="n"/>
-      <c r="F54" s="2" t="n"/>
-      <c r="G54" s="2" t="n"/>
-      <c r="H54" s="2" t="n"/>
-      <c r="I54" s="3" t="n"/>
+      <c r="I54" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="28" customHeight="1">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>LC-A01</t>
+          <t>LR-A06</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>loss_child</t>
+          <t>leaky_relu_child</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>p_rst_clears_gradient</t>
+          <t>p_sign_preserved_for_positive</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>RST</t>
+          <t>FA</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>rst |=&gt; gradient_out==0</t>
+          <t>(lr_valid_in &amp;&amp; !lr_data_in[15]) |=&gt; !lr_data_out[15]</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>Unbounded</t>
+          <t>BMC</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I55" s="8" t="inlineStr">
@@ -2949,42 +3013,42 @@
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>LC-A02</t>
+          <t>LR-A07</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>loss_child</t>
+          <t>leaky_relu_child</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>p_rst_clears_valid</t>
+          <t>p_zero_boundary</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>RST</t>
+          <t>FA</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="F56" s="11" t="inlineStr">
         <is>
-          <t>rst |=&gt; !valid_out</t>
+          <t>(lr_valid_in &amp;&amp; lr_data_in==0) |=&gt; lr_data_out==0</t>
         </is>
       </c>
       <c r="G56" s="9" t="inlineStr">
         <is>
-          <t>Unbounded</t>
+          <t>BMC</t>
         </is>
       </c>
       <c r="H56" s="9" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I56" s="8" t="inlineStr">
@@ -2996,22 +3060,22 @@
     <row r="57" ht="28" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>LC-A03</t>
+          <t>LR-A08</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>loss_child</t>
+          <t>leaky_relu_child</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>p_valid_out_registered</t>
+          <t>p_rst_clears_overflow</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>VP</t>
+          <t>RST</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -3021,17 +3085,17 @@
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>1'b1 |=&gt; valid_out==$past(valid_in)</t>
+          <t>rst |=&gt; !lr_overflow_out  [BUG-OVF-1: sticky flag cleared on reset]</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>BMC</t>
+          <t>Unbounded</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I57" s="8" t="inlineStr">
@@ -3043,225 +3107,225 @@
     <row r="58" ht="28" customHeight="1">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>LC-A04</t>
+          <t>LR-A09</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>loss_child</t>
+          <t>leaky_relu_child</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>p_valid_out_low_when_in_low</t>
+          <t>p_overflow_is_sticky</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="E58" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F58" s="11" t="inlineStr">
+        <is>
+          <t>lr_overflow_out |=&gt; lr_overflow_out  [BUG-OVF-1: once set stays set until rst]</t>
+        </is>
+      </c>
+      <c r="G58" s="9" t="inlineStr">
+        <is>
+          <t>Unbounded</t>
+        </is>
+      </c>
+      <c r="H58" s="9" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I58" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>── LRD_CHILD ──</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n"/>
+      <c r="E59" s="2" t="n"/>
+      <c r="F59" s="2" t="n"/>
+      <c r="G59" s="2" t="n"/>
+      <c r="H59" s="2" t="n"/>
+      <c r="I59" s="3" t="n"/>
+    </row>
+    <row r="60" ht="28" customHeight="1">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>LRD-A01</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>lrd_child</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>p_rst_clears_outputs</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>RST</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>rst |=&gt; (!lr_d_valid_out &amp;&amp; lr_d_data_out==0)</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>Unbounded</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I60" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="28" customHeight="1">
+      <c r="A61" s="9" t="inlineStr">
+        <is>
+          <t>LRD-A02</t>
+        </is>
+      </c>
+      <c r="B61" s="10" t="inlineStr">
+        <is>
+          <t>lrd_child</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="inlineStr">
+        <is>
+          <t>p_valid_out_mirrors_valid_in</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="inlineStr">
+        <is>
           <t>VP</t>
         </is>
       </c>
-      <c r="E58" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F58" s="11" t="inlineStr">
-        <is>
-          <t>!valid_in |=&gt; !valid_out  [data clears when invalid]</t>
-        </is>
-      </c>
-      <c r="G58" s="9" t="inlineStr">
+      <c r="E61" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F61" s="11" t="inlineStr">
+        <is>
+          <t>1'b1 |=&gt; lr_d_valid_out==$past(lr_d_valid_in)  [unconditional]</t>
+        </is>
+      </c>
+      <c r="G61" s="9" t="inlineStr">
         <is>
           <t>BMC</t>
         </is>
       </c>
-      <c r="H58" s="9" t="inlineStr">
+      <c r="H61" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I58" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="28" customHeight="1">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>LC-A05</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>loss_child</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>p_positive_gradient_when_H_gt_Y</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
-      <c r="E59" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F59" s="7" t="inlineStr">
-        <is>
-          <t>(valid_in &amp;&amp; H&gt;Y) |=&gt; !gradient_out[15]</t>
-        </is>
-      </c>
-      <c r="G59" s="5" t="inlineStr">
+      <c r="I61" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="28" customHeight="1">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>LRD-A03</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>lrd_child</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>p_data_zero_when_invalid</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>DP</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>!lr_d_valid_in |=&gt; lr_d_data_out==0</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
         <is>
           <t>BMC</t>
         </is>
       </c>
-      <c r="H59" s="5" t="inlineStr">
+      <c r="H62" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I59" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="28" customHeight="1">
-      <c r="A60" s="9" t="inlineStr">
-        <is>
-          <t>LC-A06</t>
-        </is>
-      </c>
-      <c r="B60" s="10" t="inlineStr">
-        <is>
-          <t>loss_child</t>
-        </is>
-      </c>
-      <c r="C60" s="10" t="inlineStr">
-        <is>
-          <t>p_negative_gradient_when_H_lt_Y</t>
-        </is>
-      </c>
-      <c r="D60" s="9" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
-      <c r="E60" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F60" s="11" t="inlineStr">
-        <is>
-          <t>(valid_in &amp;&amp; H&lt;Y) |=&gt; gradient_out[15]</t>
-        </is>
-      </c>
-      <c r="G60" s="9" t="inlineStr">
-        <is>
-          <t>BMC</t>
-        </is>
-      </c>
-      <c r="H60" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I60" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="28" customHeight="1">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>LC-A07</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>loss_child</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>p_zero_gradient_when_H_eq_Y</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t>(valid_in &amp;&amp; H==Y) |=&gt; gradient_out==0</t>
-        </is>
-      </c>
-      <c r="G61" s="5" t="inlineStr">
-        <is>
-          <t>BMC</t>
-        </is>
-      </c>
-      <c r="H61" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I61" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="18" customHeight="1">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>── GRADIENT_DESCENT ──</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="n"/>
-      <c r="C62" s="2" t="n"/>
-      <c r="D62" s="2" t="n"/>
-      <c r="E62" s="2" t="n"/>
-      <c r="F62" s="2" t="n"/>
-      <c r="G62" s="2" t="n"/>
-      <c r="H62" s="2" t="n"/>
-      <c r="I62" s="3" t="n"/>
+      <c r="I62" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="28" customHeight="1">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>GD-A01</t>
+          <t>LRD-A04</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>gradient_descent</t>
+          <t>lrd_child</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>p_rst_clears_output</t>
+          <t>p_positive_H_passes_gradient_through</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>RST</t>
+          <t>FA</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
@@ -3271,17 +3335,17 @@
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>rst |=&gt; value_updated_out==0</t>
+          <t>(valid_in &amp;&amp; !H[15]) |=&gt; data_out==$past(data_in)</t>
         </is>
       </c>
       <c r="G63" s="9" t="inlineStr">
         <is>
-          <t>Unbounded</t>
+          <t>BMC</t>
         </is>
       </c>
       <c r="H63" s="9" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I63" s="8" t="inlineStr">
@@ -3293,22 +3357,22 @@
     <row r="64" ht="28" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>GD-A02</t>
+          <t>LRD-A05</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>gradient_descent</t>
+          <t>lrd_child</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>p_rst_clears_done</t>
+          <t>p_negative_H_scales_gradient</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>RST</t>
+          <t>FA</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -3318,17 +3382,17 @@
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>rst |=&gt; !grad_descent_done_out</t>
+          <t>(valid_in &amp;&amp; H[15] &amp;&amp; leak!=1.0) |=&gt; data_out!=$past(data_in)</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>Unbounded</t>
+          <t>BMC</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I64" s="8" t="inlineStr">
@@ -3340,32 +3404,32 @@
     <row r="65" ht="28" customHeight="1">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>GD-A03</t>
+          <t>LRD-A06</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>gradient_descent</t>
+          <t>lrd_child</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>p_done_one_cycle_delay</t>
+          <t>p_zero_H_passes_gradient_through</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>VP</t>
+          <t>FA</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>1'b1 |=&gt; done==$past(grad_descent_valid_in)</t>
+          <t>(valid_in &amp;&amp; H==0) |=&gt; data_out==$past(data_in)</t>
         </is>
       </c>
       <c r="G65" s="9" t="inlineStr">
@@ -3375,7 +3439,7 @@
       </c>
       <c r="H65" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I65" s="8" t="inlineStr">
@@ -3387,22 +3451,22 @@
     <row r="66" ht="28" customHeight="1">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>GD-A04</t>
+          <t>LRD-A07</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>gradient_descent</t>
+          <t>lrd_child</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>p_output_stable_when_not_valid</t>
+          <t>p_rst_clears_overflow</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>DP</t>
+          <t>RST</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -3412,17 +3476,17 @@
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>!valid_in |=&gt; value_updated_out==$past(value_updated_out)  [HOLD, not clear]</t>
+          <t>rst |=&gt; !lr_d_overflow_out  [BUG-OVF-1: sticky flag cleared on reset]</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>BMC</t>
+          <t>Unbounded</t>
         </is>
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I66" s="8" t="inlineStr">
@@ -3434,17 +3498,17 @@
     <row r="67" ht="28" customHeight="1">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>GD-A05</t>
+          <t>LRD-A08</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>gradient_descent</t>
+          <t>lrd_child</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>p_weight_mode_produces_output_when_valid</t>
+          <t>p_overflow_is_sticky</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
@@ -3459,200 +3523,200 @@
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
-          <t>(valid_in &amp;&amp; weight_mode &amp;&amp; inputs!=0) |=&gt; out!=0</t>
+          <t>lr_d_overflow_out |=&gt; lr_d_overflow_out  [BUG-OVF-1: once set stays set until rst]</t>
         </is>
       </c>
       <c r="G67" s="9" t="inlineStr">
         <is>
+          <t>Unbounded</t>
+        </is>
+      </c>
+      <c r="H67" s="9" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I67" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>── LOSS_CHILD ──</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n"/>
+      <c r="C68" s="2" t="n"/>
+      <c r="D68" s="2" t="n"/>
+      <c r="E68" s="2" t="n"/>
+      <c r="F68" s="2" t="n"/>
+      <c r="G68" s="2" t="n"/>
+      <c r="H68" s="2" t="n"/>
+      <c r="I68" s="3" t="n"/>
+    </row>
+    <row r="69" ht="28" customHeight="1">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>LC-A01</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>loss_child</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>p_rst_clears_gradient</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>RST</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>rst |=&gt; gradient_out==0</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>Unbounded</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I69" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="28" customHeight="1">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>LC-A02</t>
+        </is>
+      </c>
+      <c r="B70" s="10" t="inlineStr">
+        <is>
+          <t>loss_child</t>
+        </is>
+      </c>
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t>p_rst_clears_valid</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>RST</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F70" s="11" t="inlineStr">
+        <is>
+          <t>rst |=&gt; !valid_out</t>
+        </is>
+      </c>
+      <c r="G70" s="9" t="inlineStr">
+        <is>
+          <t>Unbounded</t>
+        </is>
+      </c>
+      <c r="H70" s="9" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I70" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="28" customHeight="1">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>LC-A03</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>loss_child</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>p_valid_out_registered</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>VP</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>1'b1 |=&gt; valid_out==$past(valid_in)</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
           <t>BMC</t>
         </is>
       </c>
-      <c r="H67" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I67" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="28" customHeight="1">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>GD-A06</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>gradient_descent</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>p_done_implies_valid_was_set</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="inlineStr">
-        <is>
-          <t>VP</t>
-        </is>
-      </c>
-      <c r="E68" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F68" s="7" t="inlineStr">
-        <is>
-          <t>done |-&gt; $past(valid_in)</t>
-        </is>
-      </c>
-      <c r="G68" s="5" t="inlineStr">
-        <is>
-          <t>BMC</t>
-        </is>
-      </c>
-      <c r="H68" s="5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I68" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="28" customHeight="1">
-      <c r="A69" s="9" t="inlineStr">
-        <is>
-          <t>GD-A07</t>
-        </is>
-      </c>
-      <c r="B69" s="10" t="inlineStr">
-        <is>
-          <t>gradient_descent</t>
-        </is>
-      </c>
-      <c r="C69" s="10" t="inlineStr">
-        <is>
-          <t>p_not_done_implies_valid_was_clear</t>
-        </is>
-      </c>
-      <c r="D69" s="9" t="inlineStr">
-        <is>
-          <t>VP</t>
-        </is>
-      </c>
-      <c r="E69" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F69" s="11" t="inlineStr">
-        <is>
-          <t>!done |-&gt; !$past(valid_in)</t>
-        </is>
-      </c>
-      <c r="G69" s="9" t="inlineStr">
-        <is>
-          <t>BMC</t>
-        </is>
-      </c>
-      <c r="H69" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I69" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="28" customHeight="1">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>GD-A08</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>gradient_descent</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>p_weight_mode_descent_direction</t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
-      <c r="E70" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F70" s="7" t="inlineStr">
-        <is>
-          <t>(valid_in &amp;&amp; weight_mode &amp;&amp; pos_grad &amp;&amp; pos_lr) |=&gt; $signed(out)&lt;$signed($past(old))</t>
-        </is>
-      </c>
-      <c r="G70" s="5" t="inlineStr">
-        <is>
-          <t>BMC</t>
-        </is>
-      </c>
-      <c r="H70" s="5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I70" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="18" customHeight="1">
-      <c r="A71" s="4" t="inlineStr">
-        <is>
-          <t>── CONTROL_UNIT ──</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="n"/>
-      <c r="C71" s="2" t="n"/>
-      <c r="D71" s="2" t="n"/>
-      <c r="E71" s="2" t="n"/>
-      <c r="F71" s="2" t="n"/>
-      <c r="G71" s="2" t="n"/>
-      <c r="H71" s="2" t="n"/>
-      <c r="I71" s="3" t="n"/>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I71" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="28" customHeight="1">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>CU-A01</t>
+          <t>LC-A04</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>control_unit</t>
+          <t>loss_child</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>p_sys_switch_bit</t>
+          <t>p_data_zero_when_invalid</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>DP</t>
         </is>
       </c>
       <c r="E72" s="9" t="inlineStr">
@@ -3662,17 +3726,17 @@
       </c>
       <c r="F72" s="11" t="inlineStr">
         <is>
-          <t>sys_switch_in === instruction[0]</t>
+          <t>!valid_in |=&gt; gradient_out==0  [BUG-LC fix: gradient output cleared to 0 when input invalid]</t>
         </is>
       </c>
       <c r="G72" s="9" t="inlineStr">
         <is>
-          <t>Comb</t>
+          <t>BMC</t>
         </is>
       </c>
       <c r="H72" s="9" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I72" s="8" t="inlineStr">
@@ -3684,42 +3748,42 @@
     <row r="73" ht="28" customHeight="1">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>CU-A02</t>
+          <t>LC-A05</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>control_unit</t>
+          <t>loss_child</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>p_ub_rd_start_bit</t>
+          <t>p_positive_gradient_when_H_gt_Y</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>FA</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>ub_rd_start_in === instruction[1]</t>
+          <t>(valid_in &amp;&amp; H&gt;Y) |=&gt; !gradient_out[15]</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>Comb</t>
+          <t>BMC</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I73" s="8" t="inlineStr">
@@ -3731,42 +3795,42 @@
     <row r="74" ht="28" customHeight="1">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>CU-A03</t>
+          <t>LC-A06</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t>control_unit</t>
+          <t>loss_child</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>p_ub_rd_transpose_bit</t>
+          <t>p_negative_gradient_when_H_lt_Y</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>FA</t>
         </is>
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="F74" s="11" t="inlineStr">
         <is>
-          <t>ub_rd_transpose === instruction[2]</t>
+          <t>(valid_in &amp;&amp; H&lt;Y) |=&gt; gradient_out[15]</t>
         </is>
       </c>
       <c r="G74" s="9" t="inlineStr">
         <is>
-          <t>Comb</t>
+          <t>BMC</t>
         </is>
       </c>
       <c r="H74" s="9" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I74" s="8" t="inlineStr">
@@ -3778,42 +3842,42 @@
     <row r="75" ht="28" customHeight="1">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>CU-A04</t>
+          <t>LC-A07</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>control_unit</t>
+          <t>loss_child</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>p_ub_wr_host_valid_1_bit</t>
+          <t>p_zero_gradient_when_H_eq_Y</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>FA</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>ub_wr_host_valid_in_1 === instruction[3]</t>
+          <t>(valid_in &amp;&amp; H==Y) |=&gt; gradient_out==0</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>Comb</t>
+          <t>BMC</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I75" s="8" t="inlineStr">
@@ -3825,22 +3889,22 @@
     <row r="76" ht="28" customHeight="1">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>CU-A05</t>
+          <t>LC-A08</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>control_unit</t>
+          <t>loss_child</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>p_ub_wr_host_valid_2_bit</t>
+          <t>p_rst_clears_overflow</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>RST</t>
         </is>
       </c>
       <c r="E76" s="9" t="inlineStr">
@@ -3850,12 +3914,12 @@
       </c>
       <c r="F76" s="11" t="inlineStr">
         <is>
-          <t>ub_wr_host_valid_in_2 === instruction[4]</t>
+          <t>rst |=&gt; !loss_overflow_out  [BUG-OVF-1: sticky flag cleared on reset]</t>
         </is>
       </c>
       <c r="G76" s="9" t="inlineStr">
         <is>
-          <t>Comb</t>
+          <t>Unbounded</t>
         </is>
       </c>
       <c r="H76" s="9" t="inlineStr">
@@ -3872,22 +3936,22 @@
     <row r="77" ht="28" customHeight="1">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>CU-A06</t>
+          <t>LC-A09</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>control_unit</t>
+          <t>loss_child</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>p_ub_rd_col_size_field</t>
+          <t>p_overflow_is_sticky</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>FA</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -3897,12 +3961,12 @@
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>ub_rd_col_size === instruction[20:5]</t>
+          <t>loss_overflow_out |=&gt; loss_overflow_out  [BUG-OVF-1: once set stays set until rst]</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>Comb</t>
+          <t>Unbounded</t>
         </is>
       </c>
       <c r="H77" s="5" t="inlineStr">
@@ -3916,463 +3980,463 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="28" customHeight="1">
-      <c r="A78" s="9" t="inlineStr">
-        <is>
-          <t>CU-A07</t>
-        </is>
-      </c>
-      <c r="B78" s="10" t="inlineStr">
-        <is>
-          <t>control_unit</t>
-        </is>
-      </c>
-      <c r="C78" s="10" t="inlineStr">
-        <is>
-          <t>p_ub_rd_row_size_field</t>
-        </is>
-      </c>
-      <c r="D78" s="9" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="E78" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F78" s="11" t="inlineStr">
-        <is>
-          <t>ub_rd_row_size === instruction[36:21]</t>
-        </is>
-      </c>
-      <c r="G78" s="9" t="inlineStr">
-        <is>
-          <t>Comb</t>
-        </is>
-      </c>
-      <c r="H78" s="9" t="inlineStr">
+    <row r="78" ht="18" customHeight="1">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>── GRADIENT_DESCENT ──</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="n"/>
+      <c r="C78" s="2" t="n"/>
+      <c r="D78" s="2" t="n"/>
+      <c r="E78" s="2" t="n"/>
+      <c r="F78" s="2" t="n"/>
+      <c r="G78" s="2" t="n"/>
+      <c r="H78" s="2" t="n"/>
+      <c r="I78" s="3" t="n"/>
+    </row>
+    <row r="79" ht="28" customHeight="1">
+      <c r="A79" s="9" t="inlineStr">
+        <is>
+          <t>GD-A01</t>
+        </is>
+      </c>
+      <c r="B79" s="10" t="inlineStr">
+        <is>
+          <t>gradient_descent</t>
+        </is>
+      </c>
+      <c r="C79" s="10" t="inlineStr">
+        <is>
+          <t>p_rst_clears_output</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>RST</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F79" s="11" t="inlineStr">
+        <is>
+          <t>rst |=&gt; value_updated_out==0</t>
+        </is>
+      </c>
+      <c r="G79" s="9" t="inlineStr">
+        <is>
+          <t>Unbounded</t>
+        </is>
+      </c>
+      <c r="H79" s="9" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="I78" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="28" customHeight="1">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>CU-A08</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
-        <is>
-          <t>control_unit</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>p_ub_rd_addr_field</t>
-        </is>
-      </c>
-      <c r="D79" s="5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F79" s="7" t="inlineStr">
-        <is>
-          <t>ub_rd_addr_in === instruction[52:37]</t>
-        </is>
-      </c>
-      <c r="G79" s="5" t="inlineStr">
-        <is>
-          <t>Comb</t>
-        </is>
-      </c>
-      <c r="H79" s="5" t="inlineStr">
+      <c r="I79" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="28" customHeight="1">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>GD-A02</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>gradient_descent</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>p_rst_clears_done</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>RST</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>rst |=&gt; !grad_descent_done_out</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>Unbounded</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="I79" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="28" customHeight="1">
-      <c r="A80" s="9" t="inlineStr">
-        <is>
-          <t>CU-A09</t>
-        </is>
-      </c>
-      <c r="B80" s="10" t="inlineStr">
-        <is>
-          <t>control_unit</t>
-        </is>
-      </c>
-      <c r="C80" s="10" t="inlineStr">
-        <is>
-          <t>p_ub_ptr_select_field</t>
-        </is>
-      </c>
-      <c r="D80" s="9" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="E80" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F80" s="11" t="inlineStr">
-        <is>
-          <t>ub_ptr_select === instruction[61:53]</t>
-        </is>
-      </c>
-      <c r="G80" s="9" t="inlineStr">
-        <is>
-          <t>Comb</t>
-        </is>
-      </c>
-      <c r="H80" s="9" t="inlineStr">
+      <c r="I80" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="28" customHeight="1">
+      <c r="A81" s="9" t="inlineStr">
+        <is>
+          <t>GD-A03</t>
+        </is>
+      </c>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>gradient_descent</t>
+        </is>
+      </c>
+      <c r="C81" s="10" t="inlineStr">
+        <is>
+          <t>p_done_one_cycle_delay</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>VP</t>
+        </is>
+      </c>
+      <c r="E81" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F81" s="11" t="inlineStr">
+        <is>
+          <t>1'b1 |=&gt; done==$past(grad_descent_valid_in)</t>
+        </is>
+      </c>
+      <c r="G81" s="9" t="inlineStr">
+        <is>
+          <t>BMC</t>
+        </is>
+      </c>
+      <c r="H81" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I81" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="28" customHeight="1">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>GD-A04</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>gradient_descent</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>p_output_stable_when_not_valid</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>DP</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>!valid_in |=&gt; value_updated_out==$past(value_updated_out)  [HOLD, not clear]</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>BMC</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I82" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="28" customHeight="1">
+      <c r="A83" s="9" t="inlineStr">
+        <is>
+          <t>GD-A05</t>
+        </is>
+      </c>
+      <c r="B83" s="10" t="inlineStr">
+        <is>
+          <t>gradient_descent</t>
+        </is>
+      </c>
+      <c r="C83" s="10" t="inlineStr">
+        <is>
+          <t>p_weight_mode_produces_output_when_valid</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="E83" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F83" s="11" t="inlineStr">
+        <is>
+          <t>(valid_in &amp;&amp; weight_mode &amp;&amp; inputs!=0) |=&gt; out!=0</t>
+        </is>
+      </c>
+      <c r="G83" s="9" t="inlineStr">
+        <is>
+          <t>BMC</t>
+        </is>
+      </c>
+      <c r="H83" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I83" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="28" customHeight="1">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>GD-A06</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>gradient_descent</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>p_done_implies_valid_was_set</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>VP</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="inlineStr">
+        <is>
+          <t>done |-&gt; $past(valid_in)</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="inlineStr">
+        <is>
+          <t>BMC</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I84" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="28" customHeight="1">
+      <c r="A85" s="9" t="inlineStr">
+        <is>
+          <t>GD-A07</t>
+        </is>
+      </c>
+      <c r="B85" s="10" t="inlineStr">
+        <is>
+          <t>gradient_descent</t>
+        </is>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>p_not_done_implies_valid_was_clear</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="inlineStr">
+        <is>
+          <t>VP</t>
+        </is>
+      </c>
+      <c r="E85" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F85" s="11" t="inlineStr">
+        <is>
+          <t>!done |-&gt; !$past(valid_in)</t>
+        </is>
+      </c>
+      <c r="G85" s="9" t="inlineStr">
+        <is>
+          <t>BMC</t>
+        </is>
+      </c>
+      <c r="H85" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I85" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="28" customHeight="1">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>GD-A08</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>gradient_descent</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>p_weight_mode_descent_direction</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>(valid_in &amp;&amp; weight_mode &amp;&amp; pos_grad &amp;&amp; pos_lr) |=&gt; $signed(out)&lt;=$signed($past(old))</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="inlineStr">
+        <is>
+          <t>BMC</t>
+        </is>
+      </c>
+      <c r="H86" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I86" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="28" customHeight="1">
+      <c r="A87" s="9" t="inlineStr">
+        <is>
+          <t>GD-A09</t>
+        </is>
+      </c>
+      <c r="B87" s="10" t="inlineStr">
+        <is>
+          <t>gradient_descent</t>
+        </is>
+      </c>
+      <c r="C87" s="10" t="inlineStr">
+        <is>
+          <t>p_rst_clears_overflow</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>RST</t>
+        </is>
+      </c>
+      <c r="E87" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F87" s="11" t="inlineStr">
+        <is>
+          <t>rst |=&gt; !grad_overflow_out</t>
+        </is>
+      </c>
+      <c r="G87" s="9" t="inlineStr">
+        <is>
+          <t>Unbounded</t>
+        </is>
+      </c>
+      <c r="H87" s="9" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="I80" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="28" customHeight="1">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>CU-A10</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
-        <is>
-          <t>control_unit</t>
-        </is>
-      </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>p_host_data_1_field</t>
-        </is>
-      </c>
-      <c r="D81" s="5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="E81" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F81" s="7" t="inlineStr">
-        <is>
-          <t>ub_wr_host_data_in_1 === instruction[77:62]</t>
-        </is>
-      </c>
-      <c r="G81" s="5" t="inlineStr">
-        <is>
-          <t>Comb</t>
-        </is>
-      </c>
-      <c r="H81" s="5" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I81" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="28" customHeight="1">
-      <c r="A82" s="9" t="inlineStr">
-        <is>
-          <t>CU-A11</t>
-        </is>
-      </c>
-      <c r="B82" s="10" t="inlineStr">
-        <is>
-          <t>control_unit</t>
-        </is>
-      </c>
-      <c r="C82" s="10" t="inlineStr">
-        <is>
-          <t>p_host_data_2_field</t>
-        </is>
-      </c>
-      <c r="D82" s="9" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="E82" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F82" s="11" t="inlineStr">
-        <is>
-          <t>ub_wr_host_data_in_2 === instruction[93:78]</t>
-        </is>
-      </c>
-      <c r="G82" s="9" t="inlineStr">
-        <is>
-          <t>Comb</t>
-        </is>
-      </c>
-      <c r="H82" s="9" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I82" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="28" customHeight="1">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>CU-A12</t>
-        </is>
-      </c>
-      <c r="B83" s="6" t="inlineStr">
-        <is>
-          <t>control_unit</t>
-        </is>
-      </c>
-      <c r="C83" s="6" t="inlineStr">
-        <is>
-          <t>p_vpu_data_pathway_field</t>
-        </is>
-      </c>
-      <c r="D83" s="5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="E83" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F83" s="7" t="inlineStr">
-        <is>
-          <t>vpu_data_pathway === instruction[97:94]</t>
-        </is>
-      </c>
-      <c r="G83" s="5" t="inlineStr">
-        <is>
-          <t>Comb</t>
-        </is>
-      </c>
-      <c r="H83" s="5" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I83" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="28" customHeight="1">
-      <c r="A84" s="9" t="inlineStr">
-        <is>
-          <t>CU-A13</t>
-        </is>
-      </c>
-      <c r="B84" s="10" t="inlineStr">
-        <is>
-          <t>control_unit</t>
-        </is>
-      </c>
-      <c r="C84" s="10" t="inlineStr">
-        <is>
-          <t>p_inv_batch_size_field</t>
-        </is>
-      </c>
-      <c r="D84" s="9" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="E84" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F84" s="11" t="inlineStr">
-        <is>
-          <t>inv_batch_size_times_two_in === instruction[113:98]</t>
-        </is>
-      </c>
-      <c r="G84" s="9" t="inlineStr">
-        <is>
-          <t>Comb</t>
-        </is>
-      </c>
-      <c r="H84" s="9" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I84" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="28" customHeight="1">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>CU-A14</t>
-        </is>
-      </c>
-      <c r="B85" s="6" t="inlineStr">
-        <is>
-          <t>control_unit</t>
-        </is>
-      </c>
-      <c r="C85" s="6" t="inlineStr">
-        <is>
-          <t>p_vpu_leak_factor_field</t>
-        </is>
-      </c>
-      <c r="D85" s="5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="E85" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F85" s="7" t="inlineStr">
-        <is>
-          <t>vpu_leak_factor_in === instruction[129:114]</t>
-        </is>
-      </c>
-      <c r="G85" s="5" t="inlineStr">
-        <is>
-          <t>Comb</t>
-        </is>
-      </c>
-      <c r="H85" s="5" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I85" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="28" customHeight="1">
-      <c r="A86" s="9" t="inlineStr">
-        <is>
-          <t>CU-A15</t>
-        </is>
-      </c>
-      <c r="B86" s="10" t="inlineStr">
-        <is>
-          <t>control_unit</t>
-        </is>
-      </c>
-      <c r="C86" s="10" t="inlineStr">
-        <is>
-          <t>p_bit_field_no_overlap</t>
-        </is>
-      </c>
-      <c r="D86" s="9" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="E86" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F86" s="11" t="inlineStr">
-        <is>
-          <t>All 14 field assignments cover bits [129:0] with no gap / no overlap (structural check)</t>
-        </is>
-      </c>
-      <c r="G86" s="9" t="inlineStr">
-        <is>
-          <t>Comb</t>
-        </is>
-      </c>
-      <c r="H86" s="9" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I86" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="18" customHeight="1">
-      <c r="A87" s="4" t="inlineStr">
-        <is>
-          <t>── VPU ──</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="n"/>
-      <c r="C87" s="2" t="n"/>
-      <c r="D87" s="2" t="n"/>
-      <c r="E87" s="2" t="n"/>
-      <c r="F87" s="2" t="n"/>
-      <c r="G87" s="2" t="n"/>
-      <c r="H87" s="2" t="n"/>
-      <c r="I87" s="3" t="n"/>
+      <c r="I87" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="28" customHeight="1">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>VPU-A01</t>
+          <t>GD-A10</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>vpu</t>
+          <t>gradient_descent</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>p_rst_clears_valid_out</t>
+          <t>p_overflow_is_sticky</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>RST</t>
+          <t>FA</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -4382,160 +4446,128 @@
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
-          <t>rst |=&gt; (!vpu_valid_out_1 &amp;&amp; !vpu_valid_out_2)</t>
+          <t>grad_overflow_out |=&gt; grad_overflow_out  [sticky until rst]</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>Unbounded</t>
+          <t>BMC</t>
         </is>
       </c>
       <c r="H88" s="5" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I88" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="18" customHeight="1">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>── CONTROL_UNIT ──</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="n"/>
+      <c r="C89" s="2" t="n"/>
+      <c r="D89" s="2" t="n"/>
+      <c r="E89" s="2" t="n"/>
+      <c r="F89" s="2" t="n"/>
+      <c r="G89" s="2" t="n"/>
+      <c r="H89" s="2" t="n"/>
+      <c r="I89" s="3" t="n"/>
+    </row>
+    <row r="90" ht="28" customHeight="1">
+      <c r="A90" s="9" t="inlineStr">
+        <is>
+          <t>CU-A01</t>
+        </is>
+      </c>
+      <c r="B90" s="10" t="inlineStr">
+        <is>
+          <t>control_unit</t>
+        </is>
+      </c>
+      <c r="C90" s="10" t="inlineStr">
+        <is>
+          <t>p_sys_switch_bit</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E90" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F90" s="11" t="inlineStr">
+        <is>
+          <t>sys_switch_in === instruction[0]</t>
+        </is>
+      </c>
+      <c r="G90" s="9" t="inlineStr">
+        <is>
+          <t>Comb</t>
+        </is>
+      </c>
+      <c r="H90" s="9" t="inlineStr">
+        <is>
           <t>–</t>
         </is>
       </c>
-      <c r="I88" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="28" customHeight="1">
-      <c r="A89" s="9" t="inlineStr">
-        <is>
-          <t>VPU-A02</t>
-        </is>
-      </c>
-      <c r="B89" s="10" t="inlineStr">
-        <is>
-          <t>vpu</t>
-        </is>
-      </c>
-      <c r="C89" s="10" t="inlineStr">
-        <is>
-          <t>p_rst_clears_data_out</t>
-        </is>
-      </c>
-      <c r="D89" s="9" t="inlineStr">
-        <is>
-          <t>RST</t>
-        </is>
-      </c>
-      <c r="E89" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F89" s="11" t="inlineStr">
-        <is>
-          <t>rst |=&gt; (vpu_data_out_1==0 &amp;&amp; vpu_data_out_2==0)</t>
-        </is>
-      </c>
-      <c r="G89" s="9" t="inlineStr">
-        <is>
-          <t>Unbounded</t>
-        </is>
-      </c>
-      <c r="H89" s="9" t="inlineStr">
+      <c r="I90" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="28" customHeight="1">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>CU-A02</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>control_unit</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>p_ub_rd_start_bit</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>ub_rd_start_in === instruction[1]</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>Comb</t>
+        </is>
+      </c>
+      <c r="H91" s="5" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="I89" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="28" customHeight="1">
-      <c r="A90" s="5" t="inlineStr">
-        <is>
-          <t>VPU-A03</t>
-        </is>
-      </c>
-      <c r="B90" s="6" t="inlineStr">
-        <is>
-          <t>vpu</t>
-        </is>
-      </c>
-      <c r="C90" s="6" t="inlineStr">
-        <is>
-          <t>p_zero_pathway_reg_valid</t>
-        </is>
-      </c>
-      <c r="D90" s="5" t="inlineStr">
-        <is>
-          <t>VP</t>
-        </is>
-      </c>
-      <c r="E90" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F90" s="7" t="inlineStr">
-        <is>
-          <t>pathway==0000 |=&gt; (valid_out_1==$past(valid_in_1) &amp;&amp; valid_out_2==$past(valid_in_2))</t>
-        </is>
-      </c>
-      <c r="G90" s="5" t="inlineStr">
-        <is>
-          <t>BMC</t>
-        </is>
-      </c>
-      <c r="H90" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I90" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="28" customHeight="1">
-      <c r="A91" s="9" t="inlineStr">
-        <is>
-          <t>VPU-A04</t>
-        </is>
-      </c>
-      <c r="B91" s="10" t="inlineStr">
-        <is>
-          <t>vpu</t>
-        </is>
-      </c>
-      <c r="C91" s="10" t="inlineStr">
-        <is>
-          <t>p_zero_pathway_reg_data</t>
-        </is>
-      </c>
-      <c r="D91" s="9" t="inlineStr">
-        <is>
-          <t>DP</t>
-        </is>
-      </c>
-      <c r="E91" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F91" s="11" t="inlineStr">
-        <is>
-          <t>pathway==0000 |=&gt; (data_out_1==$past(data_in_1) &amp;&amp; data_out_2==$past(data_in_2))</t>
-        </is>
-      </c>
-      <c r="G91" s="9" t="inlineStr">
-        <is>
-          <t>BMC</t>
-        </is>
-      </c>
-      <c r="H91" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="I91" s="8" t="inlineStr">
         <is>
           <t>Open</t>
@@ -4543,44 +4575,44 @@
       </c>
     </row>
     <row r="92" ht="28" customHeight="1">
-      <c r="A92" s="5" t="inlineStr">
-        <is>
-          <t>VPU-A05</t>
-        </is>
-      </c>
-      <c r="B92" s="6" t="inlineStr">
-        <is>
-          <t>vpu</t>
-        </is>
-      </c>
-      <c r="C92" s="6" t="inlineStr">
-        <is>
-          <t>p_forward_path_3cy_latency</t>
-        </is>
-      </c>
-      <c r="D92" s="5" t="inlineStr">
-        <is>
-          <t>VP</t>
-        </is>
-      </c>
-      <c r="E92" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F92" s="7" t="inlineStr">
-        <is>
-          <t>(pathway==1100 &amp;&amp; valid_in_1) |=&gt; ##2 vpu_valid_out_1  [3 cycles: bias+lr+outreg]</t>
-        </is>
-      </c>
-      <c r="G92" s="5" t="inlineStr">
-        <is>
-          <t>BMC</t>
-        </is>
-      </c>
-      <c r="H92" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
+      <c r="A92" s="9" t="inlineStr">
+        <is>
+          <t>CU-A03</t>
+        </is>
+      </c>
+      <c r="B92" s="10" t="inlineStr">
+        <is>
+          <t>control_unit</t>
+        </is>
+      </c>
+      <c r="C92" s="10" t="inlineStr">
+        <is>
+          <t>p_ub_rd_transpose_bit</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E92" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F92" s="11" t="inlineStr">
+        <is>
+          <t>ub_rd_transpose === instruction[2]</t>
+        </is>
+      </c>
+      <c r="G92" s="9" t="inlineStr">
+        <is>
+          <t>Comb</t>
+        </is>
+      </c>
+      <c r="H92" s="9" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="I92" s="8" t="inlineStr">
@@ -4590,44 +4622,44 @@
       </c>
     </row>
     <row r="93" ht="28" customHeight="1">
-      <c r="A93" s="9" t="inlineStr">
-        <is>
-          <t>VPU-A06</t>
-        </is>
-      </c>
-      <c r="B93" s="10" t="inlineStr">
-        <is>
-          <t>vpu</t>
-        </is>
-      </c>
-      <c r="C93" s="10" t="inlineStr">
-        <is>
-          <t>p_backward_path_2cy_latency</t>
-        </is>
-      </c>
-      <c r="D93" s="9" t="inlineStr">
-        <is>
-          <t>VP</t>
-        </is>
-      </c>
-      <c r="E93" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F93" s="11" t="inlineStr">
-        <is>
-          <t>(pathway==0001 &amp;&amp; valid_in_1) |=&gt; ##1 vpu_valid_out_1  [2 cycles: lrd+outreg]</t>
-        </is>
-      </c>
-      <c r="G93" s="9" t="inlineStr">
-        <is>
-          <t>BMC</t>
-        </is>
-      </c>
-      <c r="H93" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>CU-A04</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>control_unit</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>p_ub_wr_host_valid_1_bit</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F93" s="7" t="inlineStr">
+        <is>
+          <t>ub_wr_host_valid_in_1 === instruction[3]</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>Comb</t>
+        </is>
+      </c>
+      <c r="H93" s="5" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="I93" s="8" t="inlineStr">
@@ -4637,44 +4669,44 @@
       </c>
     </row>
     <row r="94" ht="28" customHeight="1">
-      <c r="A94" s="5" t="inlineStr">
-        <is>
-          <t>VPU-A07</t>
-        </is>
-      </c>
-      <c r="B94" s="6" t="inlineStr">
-        <is>
-          <t>vpu</t>
-        </is>
-      </c>
-      <c r="C94" s="6" t="inlineStr">
-        <is>
-          <t>p_transition_path_5cy_latency</t>
-        </is>
-      </c>
-      <c r="D94" s="5" t="inlineStr">
-        <is>
-          <t>VP</t>
-        </is>
-      </c>
-      <c r="E94" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F94" s="7" t="inlineStr">
-        <is>
-          <t>(pathway==1111 &amp;&amp; valid_in_1) |=&gt; ##4 vpu_valid_out_1  [5 cycles: bias+lr+loss+lrd+outreg]</t>
-        </is>
-      </c>
-      <c r="G94" s="5" t="inlineStr">
-        <is>
-          <t>BMC</t>
-        </is>
-      </c>
-      <c r="H94" s="5" t="inlineStr">
-        <is>
-          <t>10</t>
+      <c r="A94" s="9" t="inlineStr">
+        <is>
+          <t>CU-A05</t>
+        </is>
+      </c>
+      <c r="B94" s="10" t="inlineStr">
+        <is>
+          <t>control_unit</t>
+        </is>
+      </c>
+      <c r="C94" s="10" t="inlineStr">
+        <is>
+          <t>p_ub_wr_host_valid_2_bit</t>
+        </is>
+      </c>
+      <c r="D94" s="9" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E94" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F94" s="11" t="inlineStr">
+        <is>
+          <t>ub_wr_host_valid_in_2 === instruction[4]</t>
+        </is>
+      </c>
+      <c r="G94" s="9" t="inlineStr">
+        <is>
+          <t>Comb</t>
+        </is>
+      </c>
+      <c r="H94" s="9" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="I94" s="8" t="inlineStr">
@@ -4684,44 +4716,44 @@
       </c>
     </row>
     <row r="95" ht="28" customHeight="1">
-      <c r="A95" s="9" t="inlineStr">
-        <is>
-          <t>VPU-A08</t>
-        </is>
-      </c>
-      <c r="B95" s="10" t="inlineStr">
-        <is>
-          <t>vpu</t>
-        </is>
-      </c>
-      <c r="C95" s="10" t="inlineStr">
-        <is>
-          <t>p_no_output_without_input_reg</t>
-        </is>
-      </c>
-      <c r="D95" s="9" t="inlineStr">
-        <is>
-          <t>VP</t>
-        </is>
-      </c>
-      <c r="E95" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F95" s="11" t="inlineStr">
-        <is>
-          <t>(pathway==0000 &amp;&amp; !valid_in_1) |=&gt; !vpu_valid_out_1</t>
-        </is>
-      </c>
-      <c r="G95" s="9" t="inlineStr">
-        <is>
-          <t>BMC</t>
-        </is>
-      </c>
-      <c r="H95" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>CU-A06</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>control_unit</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>p_ub_rd_col_size_field</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>ub_rd_col_size === instruction[20:5]</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="inlineStr">
+        <is>
+          <t>Comb</t>
+        </is>
+      </c>
+      <c r="H95" s="5" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="I95" s="8" t="inlineStr">
@@ -4731,44 +4763,44 @@
       </c>
     </row>
     <row r="96" ht="28" customHeight="1">
-      <c r="A96" s="5" t="inlineStr">
-        <is>
-          <t>VPU-A09</t>
-        </is>
-      </c>
-      <c r="B96" s="6" t="inlineStr">
-        <is>
-          <t>vpu</t>
-        </is>
-      </c>
-      <c r="C96" s="6" t="inlineStr">
-        <is>
-          <t>p_both_columns_valid_together</t>
-        </is>
-      </c>
-      <c r="D96" s="5" t="inlineStr">
-        <is>
-          <t>VP</t>
-        </is>
-      </c>
-      <c r="E96" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F96" s="7" t="inlineStr">
-        <is>
-          <t>(valid_in_1 &amp;&amp; valid_in_2 &amp;&amp; pathway!=0000) |=&gt; valid_out_1==valid_out_2</t>
-        </is>
-      </c>
-      <c r="G96" s="5" t="inlineStr">
-        <is>
-          <t>BMC</t>
-        </is>
-      </c>
-      <c r="H96" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
+      <c r="A96" s="9" t="inlineStr">
+        <is>
+          <t>CU-A07</t>
+        </is>
+      </c>
+      <c r="B96" s="10" t="inlineStr">
+        <is>
+          <t>control_unit</t>
+        </is>
+      </c>
+      <c r="C96" s="10" t="inlineStr">
+        <is>
+          <t>p_ub_rd_row_size_field</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E96" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F96" s="11" t="inlineStr">
+        <is>
+          <t>ub_rd_row_size === instruction[36:21]</t>
+        </is>
+      </c>
+      <c r="G96" s="9" t="inlineStr">
+        <is>
+          <t>Comb</t>
+        </is>
+      </c>
+      <c r="H96" s="9" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="I96" s="8" t="inlineStr">
@@ -4778,44 +4810,44 @@
       </c>
     </row>
     <row r="97" ht="28" customHeight="1">
-      <c r="A97" s="9" t="inlineStr">
-        <is>
-          <t>VPU-A10</t>
-        </is>
-      </c>
-      <c r="B97" s="10" t="inlineStr">
-        <is>
-          <t>vpu</t>
-        </is>
-      </c>
-      <c r="C97" s="10" t="inlineStr">
-        <is>
-          <t>p_valid_out_deasserts_after_in_drops_fwd</t>
-        </is>
-      </c>
-      <c r="D97" s="9" t="inlineStr">
-        <is>
-          <t>VP</t>
-        </is>
-      </c>
-      <c r="E97" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F97" s="11" t="inlineStr">
-        <is>
-          <t>(pathway==1100 &amp;&amp; $fell(valid_in_1)) |=&gt; ##[0:3] $fell(vpu_valid_out_1)</t>
-        </is>
-      </c>
-      <c r="G97" s="9" t="inlineStr">
-        <is>
-          <t>BMC</t>
-        </is>
-      </c>
-      <c r="H97" s="9" t="inlineStr">
-        <is>
-          <t>8</t>
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>CU-A08</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>control_unit</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>p_ub_rd_addr_field</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>ub_rd_addr_in === instruction[52:37]</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>Comb</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="I97" s="8" t="inlineStr">
@@ -4825,42 +4857,42 @@
       </c>
     </row>
     <row r="98" ht="28" customHeight="1">
-      <c r="A98" s="5" t="inlineStr">
-        <is>
-          <t>VPU-A11</t>
-        </is>
-      </c>
-      <c r="B98" s="6" t="inlineStr">
-        <is>
-          <t>vpu</t>
-        </is>
-      </c>
-      <c r="C98" s="6" t="inlineStr">
-        <is>
-          <t>p_rst_clears_last_H_cache</t>
-        </is>
-      </c>
-      <c r="D98" s="5" t="inlineStr">
-        <is>
-          <t>RST</t>
-        </is>
-      </c>
-      <c r="E98" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F98" s="7" t="inlineStr">
-        <is>
-          <t>rst |=&gt; (last_H_data_1_out==0 &amp;&amp; last_H_data_2_out==0)</t>
-        </is>
-      </c>
-      <c r="G98" s="5" t="inlineStr">
-        <is>
-          <t>Unbounded</t>
-        </is>
-      </c>
-      <c r="H98" s="5" t="inlineStr">
+      <c r="A98" s="9" t="inlineStr">
+        <is>
+          <t>CU-A09</t>
+        </is>
+      </c>
+      <c r="B98" s="10" t="inlineStr">
+        <is>
+          <t>control_unit</t>
+        </is>
+      </c>
+      <c r="C98" s="10" t="inlineStr">
+        <is>
+          <t>p_ub_ptr_select_field</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E98" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F98" s="11" t="inlineStr">
+        <is>
+          <t>ub_ptr_select === instruction[61:53]</t>
+        </is>
+      </c>
+      <c r="G98" s="9" t="inlineStr">
+        <is>
+          <t>Comb</t>
+        </is>
+      </c>
+      <c r="H98" s="9" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -4872,44 +4904,44 @@
       </c>
     </row>
     <row r="99" ht="28" customHeight="1">
-      <c r="A99" s="9" t="inlineStr">
-        <is>
-          <t>VPU-A12</t>
-        </is>
-      </c>
-      <c r="B99" s="10" t="inlineStr">
-        <is>
-          <t>vpu</t>
-        </is>
-      </c>
-      <c r="C99" s="10" t="inlineStr">
-        <is>
-          <t>p_last_H_clears_when_loss_inactive</t>
-        </is>
-      </c>
-      <c r="D99" s="9" t="inlineStr">
-        <is>
-          <t>DP</t>
-        </is>
-      </c>
-      <c r="E99" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F99" s="11" t="inlineStr">
-        <is>
-          <t>!pathway[1] |=&gt; last_H_data_1_out==0 &amp;&amp; last_H_data_2_out==0</t>
-        </is>
-      </c>
-      <c r="G99" s="9" t="inlineStr">
-        <is>
-          <t>BMC</t>
-        </is>
-      </c>
-      <c r="H99" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>CU-A10</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>control_unit</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>p_host_data_1_field</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>ub_wr_host_data_in_1 === instruction[77:62]</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>Comb</t>
+        </is>
+      </c>
+      <c r="H99" s="5" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="I99" s="8" t="inlineStr">
@@ -4919,44 +4951,44 @@
       </c>
     </row>
     <row r="100" ht="28" customHeight="1">
-      <c r="A100" s="5" t="inlineStr">
-        <is>
-          <t>VPU-A13</t>
-        </is>
-      </c>
-      <c r="B100" s="6" t="inlineStr">
-        <is>
-          <t>vpu</t>
-        </is>
-      </c>
-      <c r="C100" s="6" t="inlineStr">
-        <is>
-          <t>p_last_H_registers_when_loss_active</t>
-        </is>
-      </c>
-      <c r="D100" s="5" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
-      <c r="E100" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F100" s="7" t="inlineStr">
-        <is>
-          <t>(pathway[1] &amp;&amp; valid_in_1) |=&gt; last_H_data_1_out!=0 || last_H_data_2_out!=0</t>
-        </is>
-      </c>
-      <c r="G100" s="5" t="inlineStr">
-        <is>
-          <t>BMC</t>
-        </is>
-      </c>
-      <c r="H100" s="5" t="inlineStr">
-        <is>
-          <t>6</t>
+      <c r="A100" s="9" t="inlineStr">
+        <is>
+          <t>CU-A11</t>
+        </is>
+      </c>
+      <c r="B100" s="10" t="inlineStr">
+        <is>
+          <t>control_unit</t>
+        </is>
+      </c>
+      <c r="C100" s="10" t="inlineStr">
+        <is>
+          <t>p_host_data_2_field</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E100" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F100" s="11" t="inlineStr">
+        <is>
+          <t>ub_wr_host_data_in_2 === instruction[93:78]</t>
+        </is>
+      </c>
+      <c r="G100" s="9" t="inlineStr">
+        <is>
+          <t>Comb</t>
+        </is>
+      </c>
+      <c r="H100" s="9" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
       <c r="I100" s="8" t="inlineStr">
@@ -4965,40 +4997,72 @@
         </is>
       </c>
     </row>
-    <row r="101" ht="18" customHeight="1">
-      <c r="A101" s="4" t="inlineStr">
-        <is>
-          <t>── UNIFIED_BUFFER ──</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="n"/>
-      <c r="C101" s="2" t="n"/>
-      <c r="D101" s="2" t="n"/>
-      <c r="E101" s="2" t="n"/>
-      <c r="F101" s="2" t="n"/>
-      <c r="G101" s="2" t="n"/>
-      <c r="H101" s="2" t="n"/>
-      <c r="I101" s="3" t="n"/>
+    <row r="101" ht="28" customHeight="1">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>CU-A12</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>control_unit</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>p_vpu_data_pathway_field</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F101" s="7" t="inlineStr">
+        <is>
+          <t>vpu_data_pathway === instruction[97:94]</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>Comb</t>
+        </is>
+      </c>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I101" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="28" customHeight="1">
       <c r="A102" s="9" t="inlineStr">
         <is>
-          <t>UB-A01</t>
+          <t>CU-A13</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t>unified_buffer</t>
+          <t>control_unit</t>
         </is>
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>p_rst_clears_wr_ptr</t>
+          <t>p_inv_batch_size_field</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>RST</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E102" s="9" t="inlineStr">
@@ -5008,12 +5072,12 @@
       </c>
       <c r="F102" s="11" t="inlineStr">
         <is>
-          <t>rst |=&gt; wr_ptr==0</t>
+          <t>inv_batch_size_times_two_in === instruction[113:98]</t>
         </is>
       </c>
       <c r="G102" s="9" t="inlineStr">
         <is>
-          <t>Unbounded</t>
+          <t>Comb</t>
         </is>
       </c>
       <c r="H102" s="9" t="inlineStr">
@@ -5030,22 +5094,22 @@
     <row r="103" ht="28" customHeight="1">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>UB-A02</t>
+          <t>CU-A14</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>unified_buffer</t>
+          <t>control_unit</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>p_rst_deasserts_col_size_valid</t>
+          <t>p_vpu_leak_factor_field</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>RST</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -5055,12 +5119,12 @@
       </c>
       <c r="F103" s="7" t="inlineStr">
         <is>
-          <t>rst |=&gt; !ub_rd_col_size_valid_out</t>
+          <t>vpu_leak_factor_in === instruction[129:114]</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>Unbounded</t>
+          <t>Comb</t>
         </is>
       </c>
       <c r="H103" s="5" t="inlineStr">
@@ -5077,700 +5141,668 @@
     <row r="104" ht="28" customHeight="1">
       <c r="A104" s="9" t="inlineStr">
         <is>
-          <t>UB-A03</t>
+          <t>CU-A15</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>unified_buffer</t>
+          <t>control_unit</t>
         </is>
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>p_rst_clears_input_valid</t>
+          <t>p_bit_field_no_overlap</t>
         </is>
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E104" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F104" s="11" t="inlineStr">
+        <is>
+          <t>All 14 field assignments cover bits [129:0] with no gap / no overlap (structural check)</t>
+        </is>
+      </c>
+      <c r="G104" s="9" t="inlineStr">
+        <is>
+          <t>Comb</t>
+        </is>
+      </c>
+      <c r="H104" s="9" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I104" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>── VPU ──</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="n"/>
+      <c r="C105" s="2" t="n"/>
+      <c r="D105" s="2" t="n"/>
+      <c r="E105" s="2" t="n"/>
+      <c r="F105" s="2" t="n"/>
+      <c r="G105" s="2" t="n"/>
+      <c r="H105" s="2" t="n"/>
+      <c r="I105" s="3" t="n"/>
+    </row>
+    <row r="106" ht="28" customHeight="1">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>VPU-A01</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>vpu</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>p_rst_clears_valid_out</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
           <t>RST</t>
         </is>
       </c>
-      <c r="E104" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F104" s="11" t="inlineStr">
-        <is>
-          <t>rst |=&gt; (!ub_rd_input_valid_out_0 &amp;&amp; !ub_rd_input_valid_out_1)</t>
-        </is>
-      </c>
-      <c r="G104" s="9" t="inlineStr">
+      <c r="E106" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F106" s="7" t="inlineStr">
+        <is>
+          <t>rst |=&gt; (!vpu_valid_out_1 &amp;&amp; !vpu_valid_out_2)</t>
+        </is>
+      </c>
+      <c r="G106" s="5" t="inlineStr">
         <is>
           <t>Unbounded</t>
         </is>
       </c>
-      <c r="H104" s="9" t="inlineStr">
+      <c r="H106" s="5" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="I104" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="28" customHeight="1">
-      <c r="A105" s="5" t="inlineStr">
-        <is>
-          <t>UB-A04</t>
-        </is>
-      </c>
-      <c r="B105" s="6" t="inlineStr">
-        <is>
-          <t>unified_buffer</t>
-        </is>
-      </c>
-      <c r="C105" s="6" t="inlineStr">
-        <is>
-          <t>p_rst_clears_weight_valid</t>
-        </is>
-      </c>
-      <c r="D105" s="5" t="inlineStr">
+      <c r="I106" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="28" customHeight="1">
+      <c r="A107" s="9" t="inlineStr">
+        <is>
+          <t>VPU-A02</t>
+        </is>
+      </c>
+      <c r="B107" s="10" t="inlineStr">
+        <is>
+          <t>vpu</t>
+        </is>
+      </c>
+      <c r="C107" s="10" t="inlineStr">
+        <is>
+          <t>p_rst_clears_data_out</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="inlineStr">
         <is>
           <t>RST</t>
         </is>
       </c>
-      <c r="E105" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F105" s="7" t="inlineStr">
-        <is>
-          <t>rst |=&gt; (!ub_rd_weight_valid_out_0 &amp;&amp; !ub_rd_weight_valid_out_1)</t>
-        </is>
-      </c>
-      <c r="G105" s="5" t="inlineStr">
+      <c r="E107" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F107" s="11" t="inlineStr">
+        <is>
+          <t>rst |=&gt; (vpu_data_out_1==0 &amp;&amp; vpu_data_out_2==0)</t>
+        </is>
+      </c>
+      <c r="G107" s="9" t="inlineStr">
         <is>
           <t>Unbounded</t>
         </is>
       </c>
-      <c r="H105" s="5" t="inlineStr">
+      <c r="H107" s="9" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="I105" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="28" customHeight="1">
-      <c r="A106" s="9" t="inlineStr">
-        <is>
-          <t>UB-A05</t>
-        </is>
-      </c>
-      <c r="B106" s="10" t="inlineStr">
-        <is>
-          <t>unified_buffer</t>
-        </is>
-      </c>
-      <c r="C106" s="10" t="inlineStr">
-        <is>
-          <t>p_col_size_valid_reg_decode</t>
-        </is>
-      </c>
-      <c r="D106" s="9" t="inlineStr">
+      <c r="I107" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="28" customHeight="1">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>VPU-A03</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>vpu</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>p_zero_pathway_reg_valid</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
         <is>
           <t>VP</t>
         </is>
       </c>
-      <c r="E106" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F106" s="11" t="inlineStr">
-        <is>
-          <t>1'b1 |=&gt; col_size_valid==$past(rd_start &amp;&amp; ptr_select==9'd1)</t>
-        </is>
-      </c>
-      <c r="G106" s="9" t="inlineStr">
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F108" s="7" t="inlineStr">
+        <is>
+          <t>pathway==0000 |=&gt; (valid_out_1==$past(valid_in_1) &amp;&amp; valid_out_2==$past(valid_in_2))</t>
+        </is>
+      </c>
+      <c r="G108" s="5" t="inlineStr">
         <is>
           <t>BMC</t>
         </is>
       </c>
-      <c r="H106" s="9" t="inlineStr">
+      <c r="H108" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I108" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="28" customHeight="1">
+      <c r="A109" s="9" t="inlineStr">
+        <is>
+          <t>VPU-A04</t>
+        </is>
+      </c>
+      <c r="B109" s="10" t="inlineStr">
+        <is>
+          <t>vpu</t>
+        </is>
+      </c>
+      <c r="C109" s="10" t="inlineStr">
+        <is>
+          <t>p_zero_pathway_reg_data</t>
+        </is>
+      </c>
+      <c r="D109" s="9" t="inlineStr">
+        <is>
+          <t>DP</t>
+        </is>
+      </c>
+      <c r="E109" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F109" s="11" t="inlineStr">
+        <is>
+          <t>pathway==0000 |=&gt; (data_out_1==$past(data_in_1) &amp;&amp; data_out_2==$past(data_in_2))</t>
+        </is>
+      </c>
+      <c r="G109" s="9" t="inlineStr">
+        <is>
+          <t>BMC</t>
+        </is>
+      </c>
+      <c r="H109" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I109" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="28" customHeight="1">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>VPU-A05</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>vpu</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>p_forward_path_3cy_latency</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>VP</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F110" s="7" t="inlineStr">
+        <is>
+          <t>(pathway==1100 &amp;&amp; valid_in_1) |=&gt; ##2 vpu_valid_out_1  [3 cycles: bias+lr+outreg]</t>
+        </is>
+      </c>
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>BMC</t>
+        </is>
+      </c>
+      <c r="H110" s="5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I106" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="28" customHeight="1">
-      <c r="A107" s="5" t="inlineStr">
-        <is>
-          <t>UB-A06</t>
-        </is>
-      </c>
-      <c r="B107" s="6" t="inlineStr">
-        <is>
-          <t>unified_buffer</t>
-        </is>
-      </c>
-      <c r="C107" s="6" t="inlineStr">
-        <is>
-          <t>p_wr_ptr_increments_on_vpu_write</t>
-        </is>
-      </c>
-      <c r="D107" s="5" t="inlineStr">
+      <c r="I110" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="28" customHeight="1">
+      <c r="A111" s="9" t="inlineStr">
+        <is>
+          <t>VPU-A06</t>
+        </is>
+      </c>
+      <c r="B111" s="10" t="inlineStr">
+        <is>
+          <t>vpu</t>
+        </is>
+      </c>
+      <c r="C111" s="10" t="inlineStr">
+        <is>
+          <t>p_backward_path_2cy_latency</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>VP</t>
+        </is>
+      </c>
+      <c r="E111" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F111" s="11" t="inlineStr">
+        <is>
+          <t>(pathway==0001 &amp;&amp; valid_in_1) |=&gt; ##1 vpu_valid_out_1  [2 cycles: lrd+outreg]</t>
+        </is>
+      </c>
+      <c r="G111" s="9" t="inlineStr">
+        <is>
+          <t>BMC</t>
+        </is>
+      </c>
+      <c r="H111" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I111" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="28" customHeight="1">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>VPU-A07</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>vpu</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>p_transition_path_5cy_latency</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t>VP</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F112" s="7" t="inlineStr">
+        <is>
+          <t>(pathway==1111 &amp;&amp; valid_in_1) |=&gt; ##4 vpu_valid_out_1  [5 cycles: bias+lr+loss+lrd+outreg]</t>
+        </is>
+      </c>
+      <c r="G112" s="5" t="inlineStr">
+        <is>
+          <t>BMC</t>
+        </is>
+      </c>
+      <c r="H112" s="5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I112" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="28" customHeight="1">
+      <c r="A113" s="9" t="inlineStr">
+        <is>
+          <t>VPU-A08</t>
+        </is>
+      </c>
+      <c r="B113" s="10" t="inlineStr">
+        <is>
+          <t>vpu</t>
+        </is>
+      </c>
+      <c r="C113" s="10" t="inlineStr">
+        <is>
+          <t>p_no_output_without_input_reg</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="inlineStr">
+        <is>
+          <t>VP</t>
+        </is>
+      </c>
+      <c r="E113" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F113" s="11" t="inlineStr">
+        <is>
+          <t>(pathway==0000 &amp;&amp; !valid_in_1) |=&gt; !vpu_valid_out_1</t>
+        </is>
+      </c>
+      <c r="G113" s="9" t="inlineStr">
+        <is>
+          <t>BMC</t>
+        </is>
+      </c>
+      <c r="H113" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I113" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="28" customHeight="1">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>VPU-A09</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>vpu</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>p_both_columns_valid_together</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>VP</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F114" s="7" t="inlineStr">
+        <is>
+          <t>(valid_in_1 &amp;&amp; valid_in_2 &amp;&amp; pathway!=0000) |=&gt; valid_out_1==valid_out_2</t>
+        </is>
+      </c>
+      <c r="G114" s="5" t="inlineStr">
+        <is>
+          <t>BMC</t>
+        </is>
+      </c>
+      <c r="H114" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I114" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="28" customHeight="1">
+      <c r="A115" s="9" t="inlineStr">
+        <is>
+          <t>VPU-A10</t>
+        </is>
+      </c>
+      <c r="B115" s="10" t="inlineStr">
+        <is>
+          <t>vpu</t>
+        </is>
+      </c>
+      <c r="C115" s="10" t="inlineStr">
+        <is>
+          <t>p_valid_out_deasserts_after_in_drops_fwd</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="inlineStr">
+        <is>
+          <t>VP</t>
+        </is>
+      </c>
+      <c r="E115" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F115" s="11" t="inlineStr">
+        <is>
+          <t>(pathway==1100 &amp;&amp; $fell(valid_in_1)) |=&gt; ##[0:3] $fell(vpu_valid_out_1)</t>
+        </is>
+      </c>
+      <c r="G115" s="9" t="inlineStr">
+        <is>
+          <t>BMC</t>
+        </is>
+      </c>
+      <c r="H115" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I115" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="28" customHeight="1">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>VPU-A11</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>vpu</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>p_rst_clears_last_H_cache</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>RST</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F116" s="7" t="inlineStr">
+        <is>
+          <t>rst |=&gt; (last_H_data_1_out==0 &amp;&amp; last_H_data_2_out==0)</t>
+        </is>
+      </c>
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>Unbounded</t>
+        </is>
+      </c>
+      <c r="H116" s="5" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I116" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="28" customHeight="1">
+      <c r="A117" s="9" t="inlineStr">
+        <is>
+          <t>VPU-A12</t>
+        </is>
+      </c>
+      <c r="B117" s="10" t="inlineStr">
+        <is>
+          <t>vpu</t>
+        </is>
+      </c>
+      <c r="C117" s="10" t="inlineStr">
+        <is>
+          <t>p_last_H_clears_when_loss_inactive</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="inlineStr">
         <is>
           <t>DP</t>
         </is>
       </c>
-      <c r="E107" s="5" t="inlineStr">
+      <c r="E117" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F107" s="7" t="inlineStr">
-        <is>
-          <t>(wr_valid[0] &amp;&amp; wr_valid[1]) |=&gt; wr_ptr==$past(wr_ptr)+2  [dual-channel write, +2]</t>
-        </is>
-      </c>
-      <c r="G107" s="5" t="inlineStr">
+      <c r="F117" s="11" t="inlineStr">
+        <is>
+          <t>!pathway[1] |=&gt; last_H_data_1_out==0 &amp;&amp; last_H_data_2_out==0</t>
+        </is>
+      </c>
+      <c r="G117" s="9" t="inlineStr">
         <is>
           <t>BMC</t>
         </is>
       </c>
-      <c r="H107" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I107" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="28" customHeight="1">
-      <c r="A108" s="9" t="inlineStr">
-        <is>
-          <t>UB-A07a</t>
-        </is>
-      </c>
-      <c r="B108" s="10" t="inlineStr">
-        <is>
-          <t>unified_buffer</t>
-        </is>
-      </c>
-      <c r="C108" s="10" t="inlineStr">
-        <is>
-          <t>p_rd_input_ptr_in_range</t>
-        </is>
-      </c>
-      <c r="D108" s="9" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="E108" s="9" t="inlineStr">
+      <c r="H117" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I117" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="28" customHeight="1">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>VPU-A13</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>vpu</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>p_last_H_registers_when_loss_active</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F108" s="11" t="inlineStr">
-        <is>
-          <t>rd_input_ptr &lt; UNIFIED_BUFFER_WIDTH</t>
-        </is>
-      </c>
-      <c r="G108" s="9" t="inlineStr">
+      <c r="F118" s="7" t="inlineStr">
+        <is>
+          <t>(pathway[1] &amp;&amp; valid_in_1) |=&gt; last_H_data_1_out!=0 || last_H_data_2_out!=0</t>
+        </is>
+      </c>
+      <c r="G118" s="5" t="inlineStr">
         <is>
           <t>BMC</t>
         </is>
       </c>
-      <c r="H108" s="9" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="I108" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="28" customHeight="1">
-      <c r="A109" s="5" t="inlineStr">
-        <is>
-          <t>UB-A07b</t>
-        </is>
-      </c>
-      <c r="B109" s="6" t="inlineStr">
-        <is>
-          <t>unified_buffer</t>
-        </is>
-      </c>
-      <c r="C109" s="6" t="inlineStr">
-        <is>
-          <t>p_rd_weight_ptr_in_range</t>
-        </is>
-      </c>
-      <c r="D109" s="5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="E109" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F109" s="7" t="inlineStr">
-        <is>
-          <t>rd_weight_ptr &lt; UNIFIED_BUFFER_WIDTH</t>
-        </is>
-      </c>
-      <c r="G109" s="5" t="inlineStr">
-        <is>
-          <t>BMC</t>
-        </is>
-      </c>
-      <c r="H109" s="5" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="I109" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="28" customHeight="1">
-      <c r="A110" s="9" t="inlineStr">
-        <is>
-          <t>UB-A07c</t>
-        </is>
-      </c>
-      <c r="B110" s="10" t="inlineStr">
-        <is>
-          <t>unified_buffer</t>
-        </is>
-      </c>
-      <c r="C110" s="10" t="inlineStr">
-        <is>
-          <t>p_wr_ptr_in_range</t>
-        </is>
-      </c>
-      <c r="D110" s="9" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="E110" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F110" s="11" t="inlineStr">
-        <is>
-          <t>wr_ptr &lt; UNIFIED_BUFFER_WIDTH</t>
-        </is>
-      </c>
-      <c r="G110" s="9" t="inlineStr">
-        <is>
-          <t>BMC</t>
-        </is>
-      </c>
-      <c r="H110" s="9" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="I110" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="28" customHeight="1">
-      <c r="A111" s="5" t="inlineStr">
-        <is>
-          <t>UB-A08a</t>
-        </is>
-      </c>
-      <c r="B111" s="6" t="inlineStr">
-        <is>
-          <t>unified_buffer</t>
-        </is>
-      </c>
-      <c r="C111" s="6" t="inlineStr">
-        <is>
-          <t>p_no_vpu_host_write_collision_ch0</t>
-        </is>
-      </c>
-      <c r="D111" s="5" t="inlineStr">
-        <is>
-          <t>ME</t>
-        </is>
-      </c>
-      <c r="E111" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F111" s="7" t="inlineStr">
-        <is>
-          <t>!(ub_wr_valid_in[0] &amp;&amp; ub_wr_host_valid_in[0])</t>
-        </is>
-      </c>
-      <c r="G111" s="5" t="inlineStr">
-        <is>
-          <t>BMC</t>
-        </is>
-      </c>
-      <c r="H111" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I111" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="28" customHeight="1">
-      <c r="A112" s="9" t="inlineStr">
-        <is>
-          <t>UB-A08b</t>
-        </is>
-      </c>
-      <c r="B112" s="10" t="inlineStr">
-        <is>
-          <t>unified_buffer</t>
-        </is>
-      </c>
-      <c r="C112" s="10" t="inlineStr">
-        <is>
-          <t>p_no_vpu_host_write_collision_ch1</t>
-        </is>
-      </c>
-      <c r="D112" s="9" t="inlineStr">
-        <is>
-          <t>ME</t>
-        </is>
-      </c>
-      <c r="E112" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F112" s="11" t="inlineStr">
-        <is>
-          <t>!(ub_wr_valid_in[1] &amp;&amp; ub_wr_host_valid_in[1])</t>
-        </is>
-      </c>
-      <c r="G112" s="9" t="inlineStr">
-        <is>
-          <t>BMC</t>
-        </is>
-      </c>
-      <c r="H112" s="9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I112" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="28" customHeight="1">
-      <c r="A113" s="5" t="inlineStr">
-        <is>
-          <t>UB-A09a</t>
-        </is>
-      </c>
-      <c r="B113" s="6" t="inlineStr">
-        <is>
-          <t>unified_buffer</t>
-        </is>
-      </c>
-      <c r="C113" s="6" t="inlineStr">
-        <is>
-          <t>p_col_size_out_correct_non_transpose</t>
-        </is>
-      </c>
-      <c r="D113" s="5" t="inlineStr">
-        <is>
-          <t>DP</t>
-        </is>
-      </c>
-      <c r="E113" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F113" s="7" t="inlineStr">
-        <is>
-          <t>(col_size_valid &amp;&amp; !rd_transpose) |-&gt; col_size_out==ub_rd_col_size</t>
-        </is>
-      </c>
-      <c r="G113" s="5" t="inlineStr">
-        <is>
-          <t>BMC</t>
-        </is>
-      </c>
-      <c r="H113" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I113" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="28" customHeight="1">
-      <c r="A114" s="9" t="inlineStr">
-        <is>
-          <t>UB-A09b</t>
-        </is>
-      </c>
-      <c r="B114" s="10" t="inlineStr">
-        <is>
-          <t>unified_buffer</t>
-        </is>
-      </c>
-      <c r="C114" s="10" t="inlineStr">
-        <is>
-          <t>p_col_size_out_correct_transpose</t>
-        </is>
-      </c>
-      <c r="D114" s="9" t="inlineStr">
-        <is>
-          <t>DP</t>
-        </is>
-      </c>
-      <c r="E114" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F114" s="11" t="inlineStr">
-        <is>
-          <t>(col_size_valid &amp;&amp; rd_transpose) |-&gt; col_size_out==ub_rd_row_size</t>
-        </is>
-      </c>
-      <c r="G114" s="9" t="inlineStr">
-        <is>
-          <t>BMC</t>
-        </is>
-      </c>
-      <c r="H114" s="9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I114" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="28" customHeight="1">
-      <c r="A115" s="5" t="inlineStr">
-        <is>
-          <t>UB-A10</t>
-        </is>
-      </c>
-      <c r="B115" s="6" t="inlineStr">
-        <is>
-          <t>unified_buffer</t>
-        </is>
-      </c>
-      <c r="C115" s="6" t="inlineStr">
-        <is>
-          <t>p_col_size_out_zero_when_not_valid</t>
-        </is>
-      </c>
-      <c r="D115" s="5" t="inlineStr">
-        <is>
-          <t>DP</t>
-        </is>
-      </c>
-      <c r="E115" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F115" s="7" t="inlineStr">
-        <is>
-          <t>!col_size_valid |-&gt; col_size_out==0</t>
-        </is>
-      </c>
-      <c r="G115" s="5" t="inlineStr">
-        <is>
-          <t>BMC</t>
-        </is>
-      </c>
-      <c r="H115" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I115" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="28" customHeight="1">
-      <c r="A116" s="9" t="inlineStr">
-        <is>
-          <t>UB-A11</t>
-        </is>
-      </c>
-      <c r="B116" s="10" t="inlineStr">
-        <is>
-          <t>unified_buffer</t>
-        </is>
-      </c>
-      <c r="C116" s="10" t="inlineStr">
-        <is>
-          <t>p_rst_clears_rd_bias_ptr</t>
-        </is>
-      </c>
-      <c r="D116" s="9" t="inlineStr">
-        <is>
-          <t>RST</t>
-        </is>
-      </c>
-      <c r="E116" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F116" s="11" t="inlineStr">
-        <is>
-          <t>rst |=&gt; rd_bias_ptr==0</t>
-        </is>
-      </c>
-      <c r="G116" s="9" t="inlineStr">
-        <is>
-          <t>Unbounded</t>
-        </is>
-      </c>
-      <c r="H116" s="9" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I116" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="28" customHeight="1">
-      <c r="A117" s="5" t="inlineStr">
-        <is>
-          <t>UB-A12</t>
-        </is>
-      </c>
-      <c r="B117" s="6" t="inlineStr">
-        <is>
-          <t>unified_buffer</t>
-        </is>
-      </c>
-      <c r="C117" s="6" t="inlineStr">
-        <is>
-          <t>p_rst_clears_rd_Y_ptr</t>
-        </is>
-      </c>
-      <c r="D117" s="5" t="inlineStr">
-        <is>
-          <t>RST</t>
-        </is>
-      </c>
-      <c r="E117" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F117" s="7" t="inlineStr">
-        <is>
-          <t>rst |=&gt; rd_Y_ptr==0</t>
-        </is>
-      </c>
-      <c r="G117" s="5" t="inlineStr">
-        <is>
-          <t>Unbounded</t>
-        </is>
-      </c>
-      <c r="H117" s="5" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I117" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="28" customHeight="1">
-      <c r="A118" s="9" t="inlineStr">
-        <is>
-          <t>UB-A13</t>
-        </is>
-      </c>
-      <c r="B118" s="10" t="inlineStr">
-        <is>
-          <t>unified_buffer</t>
-        </is>
-      </c>
-      <c r="C118" s="10" t="inlineStr">
-        <is>
-          <t>p_rst_clears_rd_H_ptr</t>
-        </is>
-      </c>
-      <c r="D118" s="9" t="inlineStr">
-        <is>
-          <t>RST</t>
-        </is>
-      </c>
-      <c r="E118" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F118" s="11" t="inlineStr">
-        <is>
-          <t>rst |=&gt; rd_H_ptr==0</t>
-        </is>
-      </c>
-      <c r="G118" s="9" t="inlineStr">
-        <is>
-          <t>Unbounded</t>
-        </is>
-      </c>
-      <c r="H118" s="9" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="H118" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="I118" s="8" t="inlineStr">
@@ -5779,57 +5811,25 @@
         </is>
       </c>
     </row>
-    <row r="119" ht="28" customHeight="1">
-      <c r="A119" s="5" t="inlineStr">
-        <is>
-          <t>UB-A14</t>
-        </is>
-      </c>
-      <c r="B119" s="6" t="inlineStr">
-        <is>
-          <t>unified_buffer</t>
-        </is>
-      </c>
-      <c r="C119" s="6" t="inlineStr">
-        <is>
-          <t>p_rst_clears_rd_grad_bias_ptr</t>
-        </is>
-      </c>
-      <c r="D119" s="5" t="inlineStr">
-        <is>
-          <t>RST</t>
-        </is>
-      </c>
-      <c r="E119" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F119" s="7" t="inlineStr">
-        <is>
-          <t>rst |=&gt; rd_grad_bias_ptr==0</t>
-        </is>
-      </c>
-      <c r="G119" s="5" t="inlineStr">
-        <is>
-          <t>Unbounded</t>
-        </is>
-      </c>
-      <c r="H119" s="5" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I119" s="8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+    <row r="119" ht="18" customHeight="1">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>── UNIFIED_BUFFER ──</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="n"/>
+      <c r="C119" s="2" t="n"/>
+      <c r="D119" s="2" t="n"/>
+      <c r="E119" s="2" t="n"/>
+      <c r="F119" s="2" t="n"/>
+      <c r="G119" s="2" t="n"/>
+      <c r="H119" s="2" t="n"/>
+      <c r="I119" s="3" t="n"/>
     </row>
     <row r="120" ht="28" customHeight="1">
       <c r="A120" s="9" t="inlineStr">
         <is>
-          <t>UB-A15</t>
+          <t>UB-A01</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>p_rst_clears_rd_grad_weight_ptr</t>
+          <t>p_rst_clears_wr_ptr</t>
         </is>
       </c>
       <c r="D120" s="9" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="F120" s="11" t="inlineStr">
         <is>
-          <t>rst |=&gt; rd_grad_weight_ptr==0</t>
+          <t>rst |=&gt; wr_ptr==0</t>
         </is>
       </c>
       <c r="G120" s="9" t="inlineStr">
@@ -5876,45 +5876,985 @@
     <row r="121" ht="28" customHeight="1">
       <c r="A121" s="5" t="inlineStr">
         <is>
+          <t>UB-A02</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>unified_buffer</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>p_rst_deasserts_col_size_valid</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>RST</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F121" s="7" t="inlineStr">
+        <is>
+          <t>rst |=&gt; !ub_rd_col_size_valid_out</t>
+        </is>
+      </c>
+      <c r="G121" s="5" t="inlineStr">
+        <is>
+          <t>Unbounded</t>
+        </is>
+      </c>
+      <c r="H121" s="5" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I121" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="28" customHeight="1">
+      <c r="A122" s="9" t="inlineStr">
+        <is>
+          <t>UB-A03</t>
+        </is>
+      </c>
+      <c r="B122" s="10" t="inlineStr">
+        <is>
+          <t>unified_buffer</t>
+        </is>
+      </c>
+      <c r="C122" s="10" t="inlineStr">
+        <is>
+          <t>p_rst_clears_input_valid</t>
+        </is>
+      </c>
+      <c r="D122" s="9" t="inlineStr">
+        <is>
+          <t>RST</t>
+        </is>
+      </c>
+      <c r="E122" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F122" s="11" t="inlineStr">
+        <is>
+          <t>rst |=&gt; (!ub_rd_input_valid_out_0 &amp;&amp; !ub_rd_input_valid_out_1)</t>
+        </is>
+      </c>
+      <c r="G122" s="9" t="inlineStr">
+        <is>
+          <t>Unbounded</t>
+        </is>
+      </c>
+      <c r="H122" s="9" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I122" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="28" customHeight="1">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>UB-A04</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>unified_buffer</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>p_rst_clears_weight_valid</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>RST</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F123" s="7" t="inlineStr">
+        <is>
+          <t>rst |=&gt; (!ub_rd_weight_valid_out_0 &amp;&amp; !ub_rd_weight_valid_out_1)</t>
+        </is>
+      </c>
+      <c r="G123" s="5" t="inlineStr">
+        <is>
+          <t>Unbounded</t>
+        </is>
+      </c>
+      <c r="H123" s="5" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I123" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="28" customHeight="1">
+      <c r="A124" s="9" t="inlineStr">
+        <is>
+          <t>UB-A05</t>
+        </is>
+      </c>
+      <c r="B124" s="10" t="inlineStr">
+        <is>
+          <t>unified_buffer</t>
+        </is>
+      </c>
+      <c r="C124" s="10" t="inlineStr">
+        <is>
+          <t>p_col_size_valid_reg_decode</t>
+        </is>
+      </c>
+      <c r="D124" s="9" t="inlineStr">
+        <is>
+          <t>VP</t>
+        </is>
+      </c>
+      <c r="E124" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F124" s="11" t="inlineStr">
+        <is>
+          <t>1'b1 |=&gt; col_size_valid==$past(rd_start &amp;&amp; ptr_select==9'd1)</t>
+        </is>
+      </c>
+      <c r="G124" s="9" t="inlineStr">
+        <is>
+          <t>BMC</t>
+        </is>
+      </c>
+      <c r="H124" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I124" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="28" customHeight="1">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>UB-A06</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>unified_buffer</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>p_wr_ptr_increments_on_vpu_write</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>DP</t>
+        </is>
+      </c>
+      <c r="E125" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F125" s="7" t="inlineStr">
+        <is>
+          <t>(wr_valid[0] &amp;&amp; wr_valid[1]) |=&gt; wr_ptr==$past(wr_ptr)+2  [dual-channel write, +2]</t>
+        </is>
+      </c>
+      <c r="G125" s="5" t="inlineStr">
+        <is>
+          <t>BMC</t>
+        </is>
+      </c>
+      <c r="H125" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I125" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="28" customHeight="1">
+      <c r="A126" s="9" t="inlineStr">
+        <is>
+          <t>UB-A07a</t>
+        </is>
+      </c>
+      <c r="B126" s="10" t="inlineStr">
+        <is>
+          <t>unified_buffer</t>
+        </is>
+      </c>
+      <c r="C126" s="10" t="inlineStr">
+        <is>
+          <t>p_rd_input_ptr_in_range</t>
+        </is>
+      </c>
+      <c r="D126" s="9" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E126" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F126" s="11" t="inlineStr">
+        <is>
+          <t>rd_input_ptr &lt; UNIFIED_BUFFER_WIDTH</t>
+        </is>
+      </c>
+      <c r="G126" s="9" t="inlineStr">
+        <is>
+          <t>BMC</t>
+        </is>
+      </c>
+      <c r="H126" s="9" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="I126" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="28" customHeight="1">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>UB-A07b</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>unified_buffer</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>p_rd_weight_ptr_in_range</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F127" s="7" t="inlineStr">
+        <is>
+          <t>rd_weight_ptr &lt; UNIFIED_BUFFER_WIDTH</t>
+        </is>
+      </c>
+      <c r="G127" s="5" t="inlineStr">
+        <is>
+          <t>BMC</t>
+        </is>
+      </c>
+      <c r="H127" s="5" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="I127" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="28" customHeight="1">
+      <c r="A128" s="9" t="inlineStr">
+        <is>
+          <t>UB-A07c</t>
+        </is>
+      </c>
+      <c r="B128" s="10" t="inlineStr">
+        <is>
+          <t>unified_buffer</t>
+        </is>
+      </c>
+      <c r="C128" s="10" t="inlineStr">
+        <is>
+          <t>p_wr_ptr_in_range</t>
+        </is>
+      </c>
+      <c r="D128" s="9" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E128" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F128" s="11" t="inlineStr">
+        <is>
+          <t>wr_ptr &lt; UNIFIED_BUFFER_WIDTH</t>
+        </is>
+      </c>
+      <c r="G128" s="9" t="inlineStr">
+        <is>
+          <t>BMC</t>
+        </is>
+      </c>
+      <c r="H128" s="9" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="I128" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="28" customHeight="1">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>UB-A08a</t>
+        </is>
+      </c>
+      <c r="B129" s="6" t="inlineStr">
+        <is>
+          <t>unified_buffer</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>p_no_vpu_host_write_collision_ch0</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F129" s="7" t="inlineStr">
+        <is>
+          <t>!(ub_wr_valid_in[0] &amp;&amp; ub_wr_host_valid_in[0])</t>
+        </is>
+      </c>
+      <c r="G129" s="5" t="inlineStr">
+        <is>
+          <t>BMC</t>
+        </is>
+      </c>
+      <c r="H129" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I129" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="28" customHeight="1">
+      <c r="A130" s="9" t="inlineStr">
+        <is>
+          <t>UB-A08b</t>
+        </is>
+      </c>
+      <c r="B130" s="10" t="inlineStr">
+        <is>
+          <t>unified_buffer</t>
+        </is>
+      </c>
+      <c r="C130" s="10" t="inlineStr">
+        <is>
+          <t>p_no_vpu_host_write_collision_ch1</t>
+        </is>
+      </c>
+      <c r="D130" s="9" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="E130" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F130" s="11" t="inlineStr">
+        <is>
+          <t>!(ub_wr_valid_in[1] &amp;&amp; ub_wr_host_valid_in[1])</t>
+        </is>
+      </c>
+      <c r="G130" s="9" t="inlineStr">
+        <is>
+          <t>BMC</t>
+        </is>
+      </c>
+      <c r="H130" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I130" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="28" customHeight="1">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>UB-A09a</t>
+        </is>
+      </c>
+      <c r="B131" s="6" t="inlineStr">
+        <is>
+          <t>unified_buffer</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>p_col_size_out_correct_non_transpose</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t>DP</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F131" s="7" t="inlineStr">
+        <is>
+          <t>(col_size_valid &amp;&amp; !rd_transpose) |-&gt; col_size_out==ub_rd_col_size</t>
+        </is>
+      </c>
+      <c r="G131" s="5" t="inlineStr">
+        <is>
+          <t>BMC</t>
+        </is>
+      </c>
+      <c r="H131" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I131" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="28" customHeight="1">
+      <c r="A132" s="9" t="inlineStr">
+        <is>
+          <t>UB-A09b</t>
+        </is>
+      </c>
+      <c r="B132" s="10" t="inlineStr">
+        <is>
+          <t>unified_buffer</t>
+        </is>
+      </c>
+      <c r="C132" s="10" t="inlineStr">
+        <is>
+          <t>p_col_size_out_correct_transpose</t>
+        </is>
+      </c>
+      <c r="D132" s="9" t="inlineStr">
+        <is>
+          <t>DP</t>
+        </is>
+      </c>
+      <c r="E132" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F132" s="11" t="inlineStr">
+        <is>
+          <t>(col_size_valid &amp;&amp; rd_transpose) |-&gt; col_size_out==ub_rd_row_size</t>
+        </is>
+      </c>
+      <c r="G132" s="9" t="inlineStr">
+        <is>
+          <t>BMC</t>
+        </is>
+      </c>
+      <c r="H132" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I132" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="28" customHeight="1">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>UB-A10</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t>unified_buffer</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>p_col_size_out_zero_when_not_valid</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>DP</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F133" s="7" t="inlineStr">
+        <is>
+          <t>!col_size_valid |-&gt; col_size_out==0</t>
+        </is>
+      </c>
+      <c r="G133" s="5" t="inlineStr">
+        <is>
+          <t>BMC</t>
+        </is>
+      </c>
+      <c r="H133" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I133" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="28" customHeight="1">
+      <c r="A134" s="9" t="inlineStr">
+        <is>
+          <t>UB-A11</t>
+        </is>
+      </c>
+      <c r="B134" s="10" t="inlineStr">
+        <is>
+          <t>unified_buffer</t>
+        </is>
+      </c>
+      <c r="C134" s="10" t="inlineStr">
+        <is>
+          <t>p_rst_clears_rd_bias_ptr</t>
+        </is>
+      </c>
+      <c r="D134" s="9" t="inlineStr">
+        <is>
+          <t>RST</t>
+        </is>
+      </c>
+      <c r="E134" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F134" s="11" t="inlineStr">
+        <is>
+          <t>rst |=&gt; rd_bias_ptr==0</t>
+        </is>
+      </c>
+      <c r="G134" s="9" t="inlineStr">
+        <is>
+          <t>Unbounded</t>
+        </is>
+      </c>
+      <c r="H134" s="9" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I134" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="28" customHeight="1">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>UB-A12</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="inlineStr">
+        <is>
+          <t>unified_buffer</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>p_rst_clears_rd_Y_ptr</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>RST</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F135" s="7" t="inlineStr">
+        <is>
+          <t>rst |=&gt; rd_Y_ptr==0</t>
+        </is>
+      </c>
+      <c r="G135" s="5" t="inlineStr">
+        <is>
+          <t>Unbounded</t>
+        </is>
+      </c>
+      <c r="H135" s="5" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I135" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="28" customHeight="1">
+      <c r="A136" s="9" t="inlineStr">
+        <is>
+          <t>UB-A13</t>
+        </is>
+      </c>
+      <c r="B136" s="10" t="inlineStr">
+        <is>
+          <t>unified_buffer</t>
+        </is>
+      </c>
+      <c r="C136" s="10" t="inlineStr">
+        <is>
+          <t>p_rst_clears_rd_H_ptr</t>
+        </is>
+      </c>
+      <c r="D136" s="9" t="inlineStr">
+        <is>
+          <t>RST</t>
+        </is>
+      </c>
+      <c r="E136" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F136" s="11" t="inlineStr">
+        <is>
+          <t>rst |=&gt; rd_H_ptr==0</t>
+        </is>
+      </c>
+      <c r="G136" s="9" t="inlineStr">
+        <is>
+          <t>Unbounded</t>
+        </is>
+      </c>
+      <c r="H136" s="9" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I136" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="28" customHeight="1">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>UB-A14</t>
+        </is>
+      </c>
+      <c r="B137" s="6" t="inlineStr">
+        <is>
+          <t>unified_buffer</t>
+        </is>
+      </c>
+      <c r="C137" s="6" t="inlineStr">
+        <is>
+          <t>p_rst_clears_rd_grad_bias_ptr</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="inlineStr">
+        <is>
+          <t>RST</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F137" s="7" t="inlineStr">
+        <is>
+          <t>rst |=&gt; rd_grad_bias_ptr==0</t>
+        </is>
+      </c>
+      <c r="G137" s="5" t="inlineStr">
+        <is>
+          <t>Unbounded</t>
+        </is>
+      </c>
+      <c r="H137" s="5" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I137" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="28" customHeight="1">
+      <c r="A138" s="9" t="inlineStr">
+        <is>
+          <t>UB-A15</t>
+        </is>
+      </c>
+      <c r="B138" s="10" t="inlineStr">
+        <is>
+          <t>unified_buffer</t>
+        </is>
+      </c>
+      <c r="C138" s="10" t="inlineStr">
+        <is>
+          <t>p_rst_clears_rd_grad_weight_ptr</t>
+        </is>
+      </c>
+      <c r="D138" s="9" t="inlineStr">
+        <is>
+          <t>RST</t>
+        </is>
+      </c>
+      <c r="E138" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F138" s="11" t="inlineStr">
+        <is>
+          <t>rst |=&gt; rd_grad_weight_ptr==0</t>
+        </is>
+      </c>
+      <c r="G138" s="9" t="inlineStr">
+        <is>
+          <t>Unbounded</t>
+        </is>
+      </c>
+      <c r="H138" s="9" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I138" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="28" customHeight="1">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
           <t>UB-A16</t>
         </is>
       </c>
-      <c r="B121" s="6" t="inlineStr">
+      <c r="B139" s="6" t="inlineStr">
         <is>
           <t>unified_buffer</t>
         </is>
       </c>
-      <c r="C121" s="6" t="inlineStr">
+      <c r="C139" s="6" t="inlineStr">
         <is>
           <t>p_rst_clears_grad_descent_ptr</t>
         </is>
       </c>
-      <c r="D121" s="5" t="inlineStr">
+      <c r="D139" s="5" t="inlineStr">
         <is>
           <t>RST</t>
         </is>
       </c>
-      <c r="E121" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F121" s="7" t="inlineStr">
+      <c r="E139" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F139" s="7" t="inlineStr">
         <is>
           <t>rst |=&gt; grad_descent_ptr==0</t>
         </is>
       </c>
-      <c r="G121" s="5" t="inlineStr">
+      <c r="G139" s="5" t="inlineStr">
         <is>
           <t>Unbounded</t>
         </is>
       </c>
-      <c r="H121" s="5" t="inlineStr">
+      <c r="H139" s="5" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="I121" s="8" t="inlineStr">
+      <c r="I139" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="28" customHeight="1">
+      <c r="A140" s="9" t="inlineStr">
+        <is>
+          <t>UB-A17</t>
+        </is>
+      </c>
+      <c r="B140" s="10" t="inlineStr">
+        <is>
+          <t>unified_buffer</t>
+        </is>
+      </c>
+      <c r="C140" s="10" t="inlineStr">
+        <is>
+          <t>p_grad_descent_ptr_max_advance</t>
+        </is>
+      </c>
+      <c r="D140" s="9" t="inlineStr">
+        <is>
+          <t>DP</t>
+        </is>
+      </c>
+      <c r="E140" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F140" s="11" t="inlineStr">
+        <is>
+          <t>grad_descent_ptr &lt;= $past(grad_descent_ptr)+2  [at most 2 GD instances fire per cycle]</t>
+        </is>
+      </c>
+      <c r="G140" s="9" t="inlineStr">
+        <is>
+          <t>BMC</t>
+        </is>
+      </c>
+      <c r="H140" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I140" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="28" customHeight="1">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>UB-A18</t>
+        </is>
+      </c>
+      <c r="B141" s="6" t="inlineStr">
+        <is>
+          <t>unified_buffer</t>
+        </is>
+      </c>
+      <c r="C141" s="6" t="inlineStr">
+        <is>
+          <t>p_grad_descent_ptr_monotonic</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="inlineStr">
+        <is>
+          <t>DP</t>
+        </is>
+      </c>
+      <c r="E141" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F141" s="7" t="inlineStr">
+        <is>
+          <t>grad_descent_ptr &gt;= $past(grad_descent_ptr)  [no decrement without reset]</t>
+        </is>
+      </c>
+      <c r="G141" s="5" t="inlineStr">
+        <is>
+          <t>BMC</t>
+        </is>
+      </c>
+      <c r="H141" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I141" s="8" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5922,17 +6862,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A33:I33"/>
-    <mergeCell ref="A71:I71"/>
-    <mergeCell ref="A47:I47"/>
+    <mergeCell ref="A59:I59"/>
+    <mergeCell ref="A41:I41"/>
+    <mergeCell ref="A68:I68"/>
+    <mergeCell ref="A49:I49"/>
+    <mergeCell ref="A89:I89"/>
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A27:I27"/>
     <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A39:I39"/>
-    <mergeCell ref="A87:I87"/>
-    <mergeCell ref="A62:I62"/>
-    <mergeCell ref="A20:I20"/>
-    <mergeCell ref="A101:I101"/>
-    <mergeCell ref="A54:I54"/>
+    <mergeCell ref="A119:I119"/>
+    <mergeCell ref="A105:I105"/>
+    <mergeCell ref="A78:I78"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5944,7 +6884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6517,31 +7457,31 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>gradient_desc</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>GD_C4</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>valid_in deasserted after a run ($fell(valid_in))</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>── CONTROL_UNIT ──</t>
         </is>
       </c>
-      <c r="B38" s="2" t="n"/>
-      <c r="C38" s="3" t="n"/>
-    </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>control_unit</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>CU_C1</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>Forward pass pathway (1100)</t>
-        </is>
-      </c>
+      <c r="B39" s="2" t="n"/>
+      <c r="C39" s="3" t="n"/>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="10" t="inlineStr">
@@ -6551,12 +7491,12 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>CU_C2</t>
+          <t>CU_C1</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>Transition pathway (1111)</t>
+          <t>Forward pass pathway (1100)</t>
         </is>
       </c>
     </row>
@@ -6568,12 +7508,12 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>CU_C3</t>
+          <t>CU_C2</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Backward pass pathway (0001)</t>
+          <t>Transition pathway (1111)</t>
         </is>
       </c>
     </row>
@@ -6585,12 +7525,12 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>CU_C4</t>
+          <t>CU_C3</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>Passthrough pathway (0000)</t>
+          <t>Backward pass pathway (0001)</t>
         </is>
       </c>
     </row>
@@ -6602,12 +7542,12 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>CU_C5</t>
+          <t>CU_C4</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>sys_switch_in asserted</t>
+          <t>Passthrough pathway (0000)</t>
         </is>
       </c>
     </row>
@@ -6619,12 +7559,12 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>CU_C6</t>
+          <t>CU_C5</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>ub_rd_transpose asserted</t>
+          <t>sys_switch_in asserted</t>
         </is>
       </c>
     </row>
@@ -6636,12 +7576,12 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>CU_C7</t>
+          <t>CU_C6</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Transposed read (start &amp;&amp; transpose)</t>
+          <t>ub_rd_transpose asserted</t>
         </is>
       </c>
     </row>
@@ -6653,40 +7593,40 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>CU_C8</t>
+          <t>CU_C7</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>Bias gradient-descent pointer (ptr_sel=5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>control_unit</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>CU_C9</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>Weight gradient-descent pointer (ptr_sel=6)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+          <t>Transposed read (start &amp;&amp; transpose)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>── VPU ──</t>
         </is>
       </c>
-      <c r="B48" s="2" t="n"/>
-      <c r="C48" s="3" t="n"/>
+      <c r="B47" s="2" t="n"/>
+      <c r="C47" s="3" t="n"/>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>vpu</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>VPU_C1</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>Forward path completes (valid_out_1 seen)</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="10" t="inlineStr">
@@ -6696,12 +7636,12 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>VPU_C1</t>
+          <t>VPU_C2</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>Forward path completes (valid_out_1 seen)</t>
+          <t>Transition path completes</t>
         </is>
       </c>
     </row>
@@ -6713,12 +7653,12 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>VPU_C2</t>
+          <t>VPU_C3</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Transition path completes</t>
+          <t>Backward path completes</t>
         </is>
       </c>
     </row>
@@ -6730,12 +7670,12 @@
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>VPU_C3</t>
+          <t>VPU_C4</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>Backward path completes</t>
+          <t>Zero pathway passthrough</t>
         </is>
       </c>
     </row>
@@ -6747,40 +7687,40 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>VPU_C4</t>
+          <t>VPU_C5</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Zero pathway passthrough</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="10" t="inlineStr">
-        <is>
-          <t>vpu</t>
-        </is>
-      </c>
-      <c r="B53" s="9" t="inlineStr">
-        <is>
-          <t>VPU_C5</t>
-        </is>
-      </c>
-      <c r="C53" s="10" t="inlineStr">
-        <is>
           <t>Both channels active simultaneously</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>── UNIFIED_BUFFER ──</t>
         </is>
       </c>
-      <c r="B54" s="2" t="n"/>
-      <c r="C54" s="3" t="n"/>
+      <c r="B53" s="2" t="n"/>
+      <c r="C53" s="3" t="n"/>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>unified_buffer</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>UB_COV1</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>Full input read burst (row=2, col=2)</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
@@ -6790,12 +7730,12 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>UB_COV1</t>
+          <t>UB_COV2</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Full input read burst (row=2, col=2)</t>
+          <t>Full weight read burst</t>
         </is>
       </c>
     </row>
@@ -6807,12 +7747,12 @@
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>UB_COV2</t>
+          <t>UB_COV3</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>Full weight read burst</t>
+          <t>Host write followed by VPU write-back</t>
         </is>
       </c>
     </row>
@@ -6824,12 +7764,12 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>UB_COV3</t>
+          <t>UB_COV4</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>Host write followed by VPU write-back</t>
+          <t>Transpose read exercised</t>
         </is>
       </c>
     </row>
@@ -6841,12 +7781,12 @@
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>UB_COV4</t>
+          <t>UB_COV5</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>Transpose read exercised</t>
+          <t>Non-transpose read exercised</t>
         </is>
       </c>
     </row>
@@ -6858,12 +7798,12 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>UB_COV5</t>
+          <t>UB_COV6</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>Non-transpose read exercised</t>
+          <t>col_size_valid output asserted</t>
         </is>
       </c>
     </row>
@@ -6875,27 +7815,61 @@
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>UB_COV6</t>
+          <t>UB_COV7</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>col_size_valid output asserted</t>
+          <t>wr_ptr reaches ≥4 (2 full dual-channel write-back cycles)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>unified_buffer</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>UB_COV8</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>Both VPU channels write simultaneously (wr_valid[0] &amp;&amp; wr_valid[1])</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>unified_buffer</t>
+        </is>
+      </c>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>UB_COV9</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>grad_descent_ptr advances past zero (write-back chain exercised)</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A47:C47"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A38:C38"/>
     <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A39:C39"/>
     <mergeCell ref="A34:C34"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A53:C53"/>
     <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A54:C54"/>
     <mergeCell ref="A29:C29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7374,7 +8348,7 @@
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E3" s="9" t="n">
         <v>3</v>
@@ -7405,7 +8379,7 @@
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>7</v>
@@ -7436,7 +8410,7 @@
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>3</v>
@@ -7467,7 +8441,7 @@
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>4</v>
@@ -7498,7 +8472,7 @@
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E7" s="9" t="n">
         <v>4</v>
@@ -7529,7 +8503,7 @@
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>4</v>
@@ -7560,10 +8534,10 @@
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>6</v>
@@ -7594,7 +8568,7 @@
         <v>15</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>0</v>
@@ -7653,10 +8627,10 @@
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>32</v>
@@ -7676,10 +8650,10 @@
       <c r="B13" s="12" t="inlineStr"/>
       <c r="C13" s="12" t="inlineStr"/>
       <c r="D13" s="4" t="n">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F13" s="12" t="inlineStr"/>
       <c r="G13" s="12" t="inlineStr"/>
